--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
   <si>
     <t>Id</t>
   </si>
@@ -246,7 +246,7 @@
 すべて理想世界に生まれ変わる為に。</t>
   </si>
   <si>
-    <t>Stage.1 VR催眠コレクティブ</t>
+    <t>AD.4036 VR催眠コレクティブ</t>
   </si>
   <si>
     <t>VR史における人類最大の事件。
@@ -261,7 +261,16 @@
 詳細は一切公表されていない。</t>
   </si>
   <si>
-    <t>Stage.2 ホワイトヴェールの静寂</t>
+    <t>AD.3256 ホワイトヴェールの静寂</t>
+  </si>
+  <si>
+    <t>「失われた過去に幸あれ」
+人類の歴史は自然災害との戦いである。
+我々は幾多の災害を乗り越え今日を迎えている。
+しかしそれは歴史的な事実に他ならない。
+これら全て悪神アンリ・マユが送り出す悪魔によって起きているのだ。
+Normは悪魔を駆逐する。
+いくか迎える最期の審判を迎えるために。</t>
   </si>
   <si>
     <t>異常現象により豪雪が大和中越山間部を覆った大災害。
@@ -275,7 +284,13 @@
 命名は救助活動が駆けつけた時の様子に由来する。</t>
   </si>
   <si>
-    <t>Stage.3 北極星の大異変</t>
+    <t>AD.2869北極星の大異変</t>
+  </si>
+  <si>
+    <t>「失われた過去に幸あれ」
+Normは過去を改編する。
+霊体の魔法使い達は時間を超越し悪魔を駆逐する。
+一人でも多くの犠牲がなくなることを願って。</t>
   </si>
   <si>
     <t>北極星の位置や動きが突然変異し
@@ -288,7 +303,14 @@
 大和全土を含む全世界広域にて発生。</t>
   </si>
   <si>
-    <t>Stage.4 アソ・カタストロフ</t>
+    <t>AD.2404 アソ・カタストロフ</t>
+  </si>
+  <si>
+    <t>「失われた過去に幸あれ」
+Normは現実を修正する。
+悪魔を駆逐することは歴史修正の旅路である。
+自然災害の存在がなくなることで生命を
+未来に続く進化と調和を果たすために。</t>
   </si>
   <si>
     <t>日本の九州地方で発生した破局噴火。
@@ -300,7 +322,14 @@
 死者は火山灰降雨を原因とするものを含む</t>
   </si>
   <si>
-    <t>Stage.5 南海トラフ巨大地震</t>
+    <t>AD.2087 南海トラフ巨大地震</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「失われた過去に幸あれ」
+Normは未来を結合する。
+死者の魂は最期の審判へ続く光の橋を渡って再生する。
+悪のない悠久に続く理想世界へ導くために。
+</t>
   </si>
   <si>
     <t>日本の南東部のプレートを震源とする巨大地震。
@@ -312,7 +341,15 @@
 死者は災害関連死の他に病死・餓死も含む</t>
   </si>
   <si>
-    <t>Stage.6 最期の日</t>
+    <t>AD.2011 魂が潰えた日</t>
+  </si>
+  <si>
+    <t>「失われた過去に幸あれ」
+Normは災害を消去する。
+悪魔によって潰えた魂は救済機会を与うるに値する。
+最期の審判を迎えた終末で
+すべての悪が滅した新世界で
+永遠の生命を手に入れるか、それは貴方次第。</t>
   </si>
   <si>
     <t>大和の東海域で発生した巨大地震。
@@ -485,10 +522,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -500,7 +537,97 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,90 +641,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -613,24 +658,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -658,7 +695,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,19 +749,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,151 +869,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,21 +886,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -884,10 +906,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -917,11 +937,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -943,9 +978,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -957,145 +994,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6311,8 +6348,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="29.1818181818182" customWidth="1"/>
@@ -6340,18 +6377,19 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="234" spans="1:3">
+    <row r="3" s="1" customFormat="1" ht="409.5" spans="1:4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="208" spans="1:3">
+    <row r="4" s="1" customFormat="1" ht="409.5" spans="1:4">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6361,49 +6399,64 @@
       <c r="C4" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="195" spans="1:3">
+      <c r="D4" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="390" spans="1:4">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="169" spans="1:3">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="312" spans="1:4">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="208" spans="1:3">
+        <v>83</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="409.5" spans="1:4">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="169" spans="1:3">
+        <v>86</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="299" spans="1:4">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="169" spans="1:3">
@@ -6411,10 +6464,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="156" spans="1:3">
@@ -6422,10 +6475,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
@@ -6433,10 +6486,10 @@
         <v>10001</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
@@ -6444,10 +6497,10 @@
         <v>10002</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
@@ -6455,10 +6508,10 @@
         <v>10003</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6492,19 +6545,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -6512,13 +6565,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -6529,19 +6582,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -6549,19 +6602,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -6569,19 +6622,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -6589,13 +6642,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
@@ -6609,19 +6662,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -6629,13 +6682,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -6643,13 +6696,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -6657,13 +6710,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -6671,13 +6724,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -6685,13 +6738,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -6699,7 +6752,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -6707,7 +6760,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -6715,7 +6768,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -6723,7 +6776,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -6731,7 +6784,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -6739,7 +6792,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -6747,7 +6800,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -6755,7 +6808,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -6763,7 +6816,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -6771,7 +6824,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -6779,7 +6832,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -6787,7 +6840,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -264,7 +264,10 @@
     <t>AD.3256 ホワイトヴェールの静寂</t>
   </si>
   <si>
-    <t>「失われた過去に幸あれ」
+    <t>AD.3256 ホワイトヴェールの静寂
+&lt;概要&gt;
+異常現象により豪雪が山間部を覆った大災害。
+「失われた過去に幸あれ」
 人類の歴史は自然災害との戦いである。
 我々は幾多の災害を乗り越え今日を迎えている。
 しかしそれは歴史的な事実に他ならない。
@@ -287,7 +290,11 @@
     <t>AD.2869北極星の大異変</t>
   </si>
   <si>
-    <t>「失われた過去に幸あれ」
+    <t>AD.2869北極星の大異変
+&lt;概要&gt;
+北極星の位置や動きが突然変異し
+地球の気候や天候に大きな影響を及ぼした一連の出来事。
+「失われた過去に幸あれ」
 Normは過去を改編する。
 霊体の魔法使い達は時間を超越し悪魔を駆逐する。
 一人でも多くの犠牲がなくなることを願って。</t>
@@ -306,7 +313,11 @@
     <t>AD.2404 アソ・カタストロフ</t>
   </si>
   <si>
-    <t>「失われた過去に幸あれ」
+    <t>AD.2404 アソ・カタストロフ
+&lt;概要&gt;
+日本の九州地方で発生した破局噴火。
+火砕流が発生し、火山灰によりライフラインが完全に停止した。
+「失われた過去に幸あれ」
 Normは現実を修正する。
 悪魔を駆逐することは歴史修正の旅路である。
 自然災害の存在がなくなることで生命を
@@ -325,11 +336,14 @@
     <t>AD.2087 南海トラフ巨大地震</t>
   </si>
   <si>
-    <t xml:space="preserve">「失われた過去に幸あれ」
+    <t>AD.2087 南海トラフ巨大地震
+&lt;概要&gt;
+日本の南東部のプレートを震源とする巨大地震。
+初動による大津波の被害は少なかったが、その後の孤立集落、医療崩壊、食料不足などの原因により多くの災害関連死者が発生した。
+「失われた過去に幸あれ」
 Normは未来を結合する。
 死者の魂は最期の審判へ続く光の橋を渡って再生する。
-悪のない悠久に続く理想世界へ導くために。
-</t>
+悪のない悠久に続く理想世界へ導くために。</t>
   </si>
   <si>
     <t>日本の南東部のプレートを震源とする巨大地震。
@@ -344,7 +358,10 @@
     <t>AD.2011 魂が潰えた日</t>
   </si>
   <si>
-    <t>「失われた過去に幸あれ」
+    <t>AD.2011 魂が潰えた日
+&lt;概要&gt;
+太平洋東海域で発生した巨大地震。
+「失われた過去に幸あれ」
 Normは災害を消去する。
 悪魔によって潰えた魂は救済機会を与うるに値する。
 最期の審判を迎えた終末で
@@ -522,9 +539,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -537,7 +554,67 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,58 +628,14 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -619,17 +652,32 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -642,39 +690,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -695,7 +712,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,7 +838,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,103 +862,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,49 +892,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,17 +906,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -928,11 +939,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -954,35 +986,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -994,16 +1011,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1012,127 +1029,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -273,7 +273,7 @@
 しかしそれは歴史的な事実に他ならない。
 これら全て悪神アンリ・マユが送り出す悪魔によって起きているのだ。
 Normは悪魔を駆逐する。
-いくか迎える最期の審判を迎えるために。</t>
+いつか迎える最期の審判を迎えるために。</t>
   </si>
   <si>
     <t>異常現象により豪雪が大和中越山間部を覆った大災害。
@@ -539,10 +539,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -554,7 +554,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,8 +598,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -582,6 +627,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -591,37 +644,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -637,39 +660,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -682,16 +675,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -712,7 +712,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,97 +850,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -826,31 +862,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,37 +886,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -906,19 +906,27 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -939,17 +947,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -986,10 +988,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1011,145 +1011,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -148,10 +148,10 @@
     <t>Seek=0でランダム生成用</t>
   </si>
   <si>
-    <t>ウルフソウル</t>
-  </si>
-  <si>
     <t>リソース</t>
+  </si>
+  <si>
+    <t>バトル</t>
   </si>
   <si>
     <t>中ボス</t>
@@ -539,8 +539,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -567,14 +567,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -590,6 +582,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -600,14 +599,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -627,34 +627,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -684,14 +668,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -718,7 +718,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,31 +832,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,31 +850,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,96 +893,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,17 +921,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -947,15 +936,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -967,6 +947,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1003,6 +992,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1014,22 +1014,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1038,118 +1038,118 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>252</v>
+        <v>110</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -2439,23 +2439,23 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D4,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Resource</v>
       </c>
       <c r="F4" s="1">
         <v>100</v>
       </c>
       <c r="G4" s="1">
-        <v>1011</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -2477,17 +2477,17 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D5,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Battle</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
       </c>
       <c r="G5" s="1">
-        <v>15</v>
+        <v>1021</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="146">
   <si>
     <t>Id</t>
   </si>
@@ -82,25 +82,34 @@
     <t>UseSlot</t>
   </si>
   <si>
-    <t>1,2,3,4,5,6,7,8,9,10,11</t>
-  </si>
-  <si>
-    <t>NA_background image_3D like_404</t>
-  </si>
-  <si>
-    <t>clipart _0147</t>
-  </si>
-  <si>
-    <t>NA_background image_3D like_140</t>
-  </si>
-  <si>
-    <t>NA_background image_3D like_094</t>
-  </si>
-  <si>
-    <t>NA_Background image_Modern_012</t>
-  </si>
-  <si>
-    <t>NA_background image_3D like_365</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>stage1</t>
+  </si>
+  <si>
+    <t>stage2</t>
+  </si>
+  <si>
+    <t>stage3</t>
+  </si>
+  <si>
+    <t>stage4</t>
+  </si>
+  <si>
+    <t>stage5</t>
+  </si>
+  <si>
+    <t>stage6</t>
+  </si>
+  <si>
+    <t>stage7</t>
+  </si>
+  <si>
+    <t>stage8</t>
+  </si>
+  <si>
+    <t>stage9</t>
   </si>
   <si>
     <t>Timing</t>
@@ -238,180 +247,275 @@
     <t>Help</t>
   </si>
   <si>
-    <t>A.D.xxxx 永遠の終結と秩序の確立</t>
-  </si>
-  <si>
-    <t>人類最後の日。天から彗星が落とされる。
-熱波は三日間続き、不義者の罪は浄化された。
-すべて理想世界に生まれ変わる為に。</t>
-  </si>
-  <si>
-    <t>AD.4036 VR催眠コレクティブ</t>
-  </si>
-  <si>
-    <t>VR史における人類最大の事件。
-&lt;詳細&gt;
-何者かが世界VR管理政策期に搭載したVR脳チップを悪用し催眠術によって集団自決を引き起こした事件。
-国際指名手配されたが犯人の特定にはいたらなかった。
-&lt;死者数&gt;
-約2500
-&lt;備考&gt;
-死者は若年層に集中している。
-本当の原因は落雷によるものだが
-詳細は一切公表されていない。</t>
-  </si>
-  <si>
-    <t>AD.3256 ホワイトヴェールの静寂</t>
-  </si>
-  <si>
-    <t>AD.3256 ホワイトヴェールの静寂
-&lt;概要&gt;
-異常現象により豪雪が山間部を覆った大災害。
-「失われた過去に幸あれ」
-人類の歴史は自然災害との戦いである。
-我々は幾多の災害を乗り越え今日を迎えている。
-しかしそれは歴史的な事実に他ならない。
-これら全て悪神アンリ・マユが送り出す悪魔によって起きているのだ。
-Normは悪魔を駆逐する。
-いつか迎える最期の審判を迎えるために。</t>
-  </si>
-  <si>
-    <t>異常現象により豪雪が大和中越山間部を覆った大災害。
-&lt;詳細&gt;
-大雪により多くの建物が雪の重みに耐え切れず倒壊。
-交通は寸断され救助活動が遅れ
-孤立した地域では命を落とす者が相次いだ。
-&lt;死者数&gt;
-約5万超
-&lt;備考&gt;
-命名は救助活動が駆けつけた時の様子に由来する。</t>
-  </si>
-  <si>
-    <t>AD.2869北極星の大異変</t>
-  </si>
-  <si>
-    <t>AD.2869北極星の大異変
-&lt;概要&gt;
-北極星の位置や動きが突然変異し
-地球の気候や天候に大きな影響を及ぼした一連の出来事。
-「失われた過去に幸あれ」
-Normは過去を改編する。
-霊体の魔法使い達は時間を超越し悪魔を駆逐する。
-一人でも多くの犠牲がなくなることを願って。</t>
-  </si>
-  <si>
-    <t>北極星の位置や動きが突然変異し
-地球の気候や天候に大きな影響を及ぼした一連の出来事。
-&lt;詳細&gt;
-海面上昇や地殻変動が活発化し地震や火山噴火が頻発した。
-&lt;死者数&gt;
-約3万
-&lt;備考&gt;
-大和全土を含む全世界広域にて発生。</t>
-  </si>
-  <si>
-    <t>AD.2404 アソ・カタストロフ</t>
-  </si>
-  <si>
-    <t>AD.2404 アソ・カタストロフ
-&lt;概要&gt;
-日本の九州地方で発生した破局噴火。
-火砕流が発生し、火山灰によりライフラインが完全に停止した。
-「失われた過去に幸あれ」
-Normは現実を修正する。
-悪魔を駆逐することは歴史修正の旅路である。
-自然災害の存在がなくなることで生命を
-未来に続く進化と調和を果たすために。</t>
-  </si>
-  <si>
-    <t>日本の九州地方で発生した破局噴火。
-&lt;詳細&gt;
-火砕流が発生し、火山灰によりライフラインが完全に停止した。
-&lt;死者数&gt;
-約7万
-&lt;備考&gt;
-死者は火山灰降雨を原因とするものを含む</t>
-  </si>
-  <si>
-    <t>AD.2087 南海トラフ巨大地震</t>
-  </si>
-  <si>
-    <t>AD.2087 南海トラフ巨大地震
-&lt;概要&gt;
-日本の南東部のプレートを震源とする巨大地震。
-初動による大津波の被害は少なかったが、その後の孤立集落、医療崩壊、食料不足などの原因により多くの災害関連死者が発生した。
-「失われた過去に幸あれ」
-Normは未来を結合する。
-死者の魂は最期の審判へ続く光の橋を渡って再生する。
-悪のない悠久に続く理想世界へ導くために。</t>
-  </si>
-  <si>
-    <t>日本の南東部のプレートを震源とする巨大地震。
-&lt;詳細&gt;
-初動による大津波の被害は少なかったが、その後の孤立集落、医療崩壊、食料不足などの原因により多くの災害関連死者が発生した。
-&lt;死者数&gt;
-約25万
-&lt;備考&gt;
-死者は災害関連死の他に病死・餓死も含む</t>
-  </si>
-  <si>
-    <t>AD.2011 魂が潰えた日</t>
-  </si>
-  <si>
-    <t>AD.2011 魂が潰えた日
-&lt;概要&gt;
-太平洋東海域で発生した巨大地震。
-「失われた過去に幸あれ」
-Normは災害を消去する。
-悪魔によって潰えた魂は救済機会を与うるに値する。
-最期の審判を迎えた終末で
-すべての悪が滅した新世界で
-永遠の生命を手に入れるか、それは貴方次第。</t>
-  </si>
-  <si>
-    <t>大和の東海域で発生した巨大地震。
-&lt;詳細&gt;
-地震により大きな揺れや大津波・火災などにより多くの被害をもたらした。
-&lt;死者数&gt;
-約2万
-&lt;備考&gt;
-死者は震災関連死も含む</t>
-  </si>
-  <si>
-    <t>A.D.1995 阪神・淡路大震災</t>
-  </si>
-  <si>
-    <t>日本の東海地方で発生した巨大地震。
-&lt;詳細&gt;
-大都市の直下で発生した「都市直下型地震」によりライフラインに深刻な被害を与えた。
-&lt;死者数&gt;
-約7300
-&lt;備考&gt;
-淡路島を震源とする</t>
-  </si>
-  <si>
-    <t>A.D.1923 関東大震災</t>
-  </si>
-  <si>
-    <t>日本の関東地方で発生した巨大地震。
-&lt;詳細&gt;
-地震により家屋の倒壊が強風により火災が広範囲に発生した。
-&lt;死者数&gt;
-約10万超
-&lt;備考&gt;
-死者は行方不明者も含む</t>
-  </si>
-  <si>
-    <t>??????</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>回路を解析し使途を殲滅する</t>
-  </si>
-  <si>
-    <t>救済執行に成功しつづける</t>
+    <t>ダミー</t>
+  </si>
+  <si>
+    <t>長針を追いかけて</t>
+  </si>
+  <si>
+    <t>思い出の光景は、時間と共に塗り替えられた。\n突如現れた魔者からリジェ達は脱出を図る。</t>
+  </si>
+  <si>
+    <t>降りる帳と地下扉</t>
+  </si>
+  <si>
+    <r>
+      <t>防衛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>システムが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>起動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、逃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>げ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地下道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ミシェルに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>先導</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>され</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>リジェ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暗闇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>進</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>む</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>窓の雨をながめて</t>
+  </si>
+  <si>
+    <t>屋根を叩く雨の音に目を覚ます。\n防衛システムを解除する為に動力室へと向かう。</t>
+  </si>
+  <si>
+    <t>桜なごりの学舎</t>
+  </si>
+  <si>
+    <t>桜が舞う学舎に魔法が飛び交った。\n魔者が消えるまで戦いは終わらない。</t>
+  </si>
+  <si>
+    <t>花びらを胸に抱いて</t>
+  </si>
+  <si>
+    <t>校内に残された魔者はあと僅か。\n平穏を取り戻すため、魔法使いは今日も戦う。</t>
+  </si>
+  <si>
+    <t>シンデレラガール</t>
+  </si>
+  <si>
+    <t>魔者、魔法使い、軍の退却……\n思惑が錯綜する中、魔女狩りが開始される。</t>
+  </si>
+  <si>
+    <t>からたちの花たち</t>
+  </si>
+  <si>
+    <t>降り立った。忘れられた地に。\nそこに広がっていたものは夢ではなかった。</t>
+  </si>
+  <si>
+    <t>うたかたの光芒</t>
+  </si>
+  <si>
+    <t>集落に残る遺産は面影か泡沫か。\nルネに先導され向かった先には……</t>
+  </si>
+  <si>
+    <t>リヴァイアサン</t>
+  </si>
+  <si>
+    <t>新しい船、美しい海、遙かなる島\n揺れる航路に棲まう嵐を越えて行く。</t>
+  </si>
+  <si>
+    <t>重なる夢と月明かり</t>
+  </si>
+  <si>
+    <t>故郷に戻ったリジェ達は\n港で行われる祭りを手伝うことに……</t>
+  </si>
+  <si>
+    <t>過ち色の記憶</t>
+  </si>
+  <si>
+    <t>三年の月日は、自分には長すぎて……\n故郷を取り戻すため、リジェ達は館に赴く。</t>
+  </si>
+  <si>
+    <t>灯籠をみずに流して</t>
+  </si>
+  <si>
+    <t>全て、答えを手にするために。\n再度、魔法学校へ侵入を試みる。</t>
+  </si>
+  <si>
+    <t>なほあまりある今</t>
+  </si>
+  <si>
+    <t>櫻の樹の下に埋まっていたものは……\n研究室に残る魔者を退け、奥へと突き進む。</t>
+  </si>
+  <si>
+    <t>ひびかけ色のキセキ</t>
+  </si>
+  <si>
+    <t>信頼できる仲間が側にいるから。\n魔法使い達は元凶である黒水晶を探し求める。</t>
+  </si>
+  <si>
+    <t>旅路の果て</t>
+  </si>
+  <si>
+    <t>魔法があれば何でも出来ると思っていたんだ。\n仲間と逸れたソラとミシェルが見たものは……</t>
   </si>
   <si>
     <t>なし</t>
@@ -539,17 +643,44 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -567,13 +698,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -582,8 +706,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -592,36 +732,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -642,9 +752,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -659,7 +776,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -668,17 +785,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -690,11 +806,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10.5"/>
+      <name val="ＭＳ ゴシック"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -712,19 +826,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,31 +874,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,25 +898,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,25 +946,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,31 +970,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,13 +994,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,41 +1035,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -975,11 +1059,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -989,6 +1088,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1011,7 +1125,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1020,7 +1134,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1029,131 +1143,131 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1161,6 +1275,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1494,8 +1611,9 @@
   <dimension ref="A1:T11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
-    <col min="5" max="5" width="8.72727272727273" style="3"/>
-    <col min="6" max="6" width="8.72727272727273" style="4"/>
+    <col min="3" max="3" width="8.45454545454546" customWidth="1"/>
+    <col min="5" max="5" width="8.72727272727273" style="4"/>
+    <col min="6" max="6" width="8.72727272727273" style="5"/>
     <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1515,7 +1633,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1577,11 +1695,11 @@
       <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <v>-1</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
+      <c r="G2" s="1">
+        <v>3</v>
       </c>
       <c r="H2" s="1">
         <v>15</v>
@@ -1593,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1">
         <v>80</v>
@@ -1625,10 +1743,10 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:20">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>10001</v>
@@ -1639,11 +1757,11 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="6">
         <v>-1</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
+      <c r="G3" s="1">
+        <v>3</v>
       </c>
       <c r="H3" s="1">
         <v>15</v>
@@ -1687,10 +1805,10 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:20">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1">
         <v>10001</v>
@@ -1699,13 +1817,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6">
         <v>-1</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
+      <c r="G4" s="1">
+        <v>3</v>
       </c>
       <c r="H4" s="1">
         <v>15</v>
@@ -1749,10 +1867,10 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:20">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>10001</v>
@@ -1761,13 +1879,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>20</v>
-      </c>
-      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
         <v>-1</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
+      <c r="G5" s="1">
+        <v>3</v>
       </c>
       <c r="H5" s="1">
         <v>15</v>
@@ -1811,10 +1929,10 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:20">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1">
         <v>10001</v>
@@ -1823,13 +1941,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5">
+        <v>6</v>
+      </c>
+      <c r="F6" s="6">
         <v>-1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>20</v>
+      <c r="G6" s="1">
+        <v>3</v>
       </c>
       <c r="H6" s="1">
         <v>15</v>
@@ -1873,10 +1991,10 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:20">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1">
         <v>10001</v>
@@ -1885,13 +2003,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6">
         <v>-1</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>20</v>
+      <c r="G7" s="1">
+        <v>3</v>
       </c>
       <c r="H7" s="1">
         <v>15</v>
@@ -1935,10 +2053,10 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:20">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1">
         <v>10001</v>
@@ -1947,13 +2065,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>50</v>
-      </c>
-      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6">
         <v>-1</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>20</v>
+      <c r="G8" s="1">
+        <v>3</v>
       </c>
       <c r="H8" s="1">
         <v>15</v>
@@ -1997,10 +2115,10 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:20">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1">
         <v>10001</v>
@@ -2009,13 +2127,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>60</v>
-      </c>
-      <c r="F9" s="5">
+        <v>12</v>
+      </c>
+      <c r="F9" s="6">
         <v>-1</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>20</v>
+      <c r="G9" s="1">
+        <v>3</v>
       </c>
       <c r="H9" s="1">
         <v>15</v>
@@ -2027,7 +2145,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L9" s="1">
         <v>80</v>
@@ -2059,10 +2177,10 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:20">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1">
         <v>10001</v>
@@ -2071,13 +2189,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>70</v>
-      </c>
-      <c r="F10" s="5">
+        <v>14</v>
+      </c>
+      <c r="F10" s="6">
         <v>-1</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>20</v>
+      <c r="G10" s="1">
+        <v>3</v>
       </c>
       <c r="H10" s="1">
         <v>15</v>
@@ -2089,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1">
         <v>80</v>
@@ -2121,25 +2239,25 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:20">
       <c r="A11" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1">
         <v>10001</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5">
+        <v>16</v>
+      </c>
+      <c r="F11" s="6">
         <v>-1</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>20</v>
+      <c r="G11" s="1">
+        <v>3</v>
       </c>
       <c r="H11" s="1">
         <v>15</v>
@@ -2151,7 +2269,7 @@
         <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L11" s="1">
         <v>80</v>
@@ -2205,22 +2323,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -2324,29 +2442,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2379,20 +2497,20 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -2423,14 +2541,14 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2461,14 +2579,14 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2499,14 +2617,14 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2537,14 +2655,14 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2575,14 +2693,14 @@
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1">
         <v>4</v>
@@ -2613,14 +2731,14 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>4</v>
@@ -2651,14 +2769,14 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
@@ -2689,14 +2807,14 @@
         <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>5</v>
@@ -2727,14 +2845,14 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>6</v>
@@ -2765,14 +2883,14 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1">
         <v>7</v>
@@ -2803,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2841,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2951,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2989,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3027,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -3065,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3103,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3141,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3179,7 +3297,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3253,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3291,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3329,7 +3447,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3367,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -3405,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3443,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3481,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3519,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -3557,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3739,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -3849,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -3887,7 +4005,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -3961,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -3999,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -4037,7 +4155,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -4075,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -4113,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M48" s="1"/>
     </row>
@@ -4150,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -4188,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -4226,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -4264,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -4446,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4556,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -4594,7 +4712,7 @@
         <v>2</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -4668,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -4706,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -4744,7 +4862,7 @@
         <v>2</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -4782,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -4820,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -4858,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -4896,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -4934,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -4972,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -5010,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -5048,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -5230,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
@@ -5340,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -5378,7 +5496,7 @@
         <v>2</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -5452,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
@@ -5490,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
@@ -5528,7 +5646,7 @@
         <v>2</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
@@ -5566,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -5602,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -5640,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -5676,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -5712,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -5748,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -5784,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -5820,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5837,25 +5955,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6338,22 +6456,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6483,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -6377,66 +6495,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="78" spans="1:3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:3">
       <c r="A2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="409.5" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="39" spans="1:4">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="409.5" spans="1:4">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="37.5" spans="1:4">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="390" spans="1:4">
+      <c r="C4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="39" spans="1:4">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="312" spans="1:4">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="39" spans="1:4">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>82</v>
@@ -6444,91 +6558,129 @@
       <c r="C6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="39" spans="1:4">
+      <c r="A7" s="1">
+        <v>50</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="409.5" spans="1:4">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="39" spans="1:4">
+      <c r="A8" s="1">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="299" spans="1:4">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="39" spans="1:3">
+      <c r="A9" s="1">
+        <v>70</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="10" s="1" customFormat="1" ht="39" spans="1:3">
+      <c r="A10" s="1">
+        <v>80</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="169" spans="1:3">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="156" spans="1:3">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="1">
-        <v>10001</v>
+        <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
       <c r="A12" s="1">
-        <v>10002</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="1">
-        <v>10003</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
+        <v>120</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>96</v>
+      <c r="C14" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>140</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6548,13 +6700,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:10">
@@ -6562,19 +6714,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -6582,13 +6734,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -6599,19 +6751,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -6619,19 +6771,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -6639,19 +6791,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -6659,13 +6811,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
@@ -6679,19 +6831,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -6699,13 +6851,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -6713,13 +6865,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -6727,13 +6879,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -6741,13 +6893,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -6755,13 +6907,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -6769,7 +6921,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -6777,7 +6929,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -6785,7 +6937,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -6793,7 +6945,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -6801,7 +6953,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -6809,7 +6961,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -6817,7 +6969,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -6825,7 +6977,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -6833,7 +6985,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -6841,7 +6993,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -6849,7 +7001,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -6857,7 +7009,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -260,6 +260,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
       <t>防衛</t>
     </r>
     <r>
@@ -643,10 +648,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -663,44 +668,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -714,16 +689,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -744,6 +726,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -752,16 +741,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -791,16 +789,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -826,19 +831,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -850,37 +861,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,7 +909,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -910,13 +939,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -928,67 +999,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1004,12 +1015,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1017,6 +1022,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1031,30 +1045,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1079,6 +1069,21 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1125,16 +1130,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1146,124 +1151,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2557,17 +2562,17 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D4,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Battle</v>
       </c>
       <c r="F4" s="1">
         <v>100</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>1011</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="132">
   <si>
     <t>Id</t>
   </si>
@@ -37,81 +37,54 @@
     <t>StageLv</t>
   </si>
   <si>
+    <t>InitMembers</t>
+  </si>
+  <si>
+    <t>RandomTroopCount</t>
+  </si>
+  <si>
+    <t>BGMId</t>
+  </si>
+  <si>
+    <t>BossBGMId</t>
+  </si>
+  <si>
+    <t>BackGround</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>stage1</t>
+  </si>
+  <si>
+    <t>stage2</t>
+  </si>
+  <si>
+    <t>stage3</t>
+  </si>
+  <si>
+    <t>stage4</t>
+  </si>
+  <si>
+    <t>stage5</t>
+  </si>
+  <si>
+    <t>stage6</t>
+  </si>
+  <si>
+    <t>stage7</t>
+  </si>
+  <si>
+    <t>stage8</t>
+  </si>
+  <si>
+    <t>stage9</t>
+  </si>
+  <si>
     <t>Turns</t>
   </si>
   <si>
-    <t>InitMembers</t>
-  </si>
-  <si>
-    <t>RandomTroopCount</t>
-  </si>
-  <si>
-    <t>BGMId</t>
-  </si>
-  <si>
-    <t>BossBGMId</t>
-  </si>
-  <si>
-    <t>BackGround</t>
-  </si>
-  <si>
-    <t>StageRect</t>
-  </si>
-  <si>
-    <t>Reborn</t>
-  </si>
-  <si>
-    <t>Alcana</t>
-  </si>
-  <si>
-    <t>SaveLimit</t>
-  </si>
-  <si>
-    <t>ContinueLimit</t>
-  </si>
-  <si>
-    <t>RankingStage</t>
-  </si>
-  <si>
-    <t>SlotSave</t>
-  </si>
-  <si>
-    <t>SubordinateValue</t>
-  </si>
-  <si>
-    <t>UseSlot</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>stage1</t>
-  </si>
-  <si>
-    <t>stage2</t>
-  </si>
-  <si>
-    <t>stage3</t>
-  </si>
-  <si>
-    <t>stage4</t>
-  </si>
-  <si>
-    <t>stage5</t>
-  </si>
-  <si>
-    <t>stage6</t>
-  </si>
-  <si>
-    <t>stage7</t>
-  </si>
-  <si>
-    <t>stage8</t>
-  </si>
-  <si>
-    <t>stage9</t>
-  </si>
-  <si>
     <t>Timing</t>
   </si>
   <si>
@@ -157,52 +130,34 @@
     <t>Seek=0でランダム生成用</t>
   </si>
   <si>
-    <t>リソース</t>
-  </si>
-  <si>
-    <t>バトル</t>
+    <t>火属性ランダムドロップ</t>
+  </si>
+  <si>
+    <t>雷属性ランダムドロップ</t>
+  </si>
+  <si>
+    <t>氷属性ランダムドロップ</t>
+  </si>
+  <si>
+    <t>光属性ランダムドロップ</t>
+  </si>
+  <si>
+    <t>闇属性ランダムドロップ</t>
   </si>
   <si>
     <t>中ボス</t>
   </si>
   <si>
-    <t>エクステンド</t>
-  </si>
-  <si>
-    <t>アーマーコード</t>
-  </si>
-  <si>
-    <t>ホープフルアイリス</t>
-  </si>
-  <si>
-    <t>イーグルアイ</t>
+    <t>中ボスハード</t>
+  </si>
+  <si>
+    <t>魔法ランダムランク10</t>
   </si>
   <si>
     <t>ボス戦</t>
   </si>
   <si>
     <t>仲間選択 3人までランダム</t>
-  </si>
-  <si>
-    <t>火属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>雷属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>氷属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>光属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>闇属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>中ボスハード</t>
-  </si>
-  <si>
-    <t>魔法ランダムランク10</t>
   </si>
   <si>
     <t>レリック</t>
@@ -568,6 +523,9 @@
     <t>アルカナフラグを管理</t>
   </si>
   <si>
+    <t>Alcana</t>
+  </si>
+  <si>
     <t>Tactics開始(UI表示前)</t>
   </si>
   <si>
@@ -648,10 +606,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -668,24 +626,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -697,7 +640,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -719,8 +662,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -728,6 +672,28 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -750,26 +716,26 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -783,15 +749,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -804,19 +769,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="ＭＳ ゴシック"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -825,13 +783,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,31 +879,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -897,121 +957,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,15 +974,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1064,15 +1007,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1084,15 +1018,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1114,11 +1039,38 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1130,149 +1082,149 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1286,12 +1238,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1613,16 +1559,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="8.45454545454546" customWidth="1"/>
     <col min="5" max="5" width="8.72727272727273" style="4"/>
-    <col min="6" max="6" width="8.72727272727273" style="5"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1583,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1653,38 +1598,8 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:20">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1700,53 +1615,23 @@
       <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
-        <v>-1</v>
+      <c r="F2" s="1">
+        <v>3</v>
       </c>
       <c r="G2" s="1">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1">
         <v>3</v>
       </c>
-      <c r="H2" s="1">
-        <v>15</v>
-      </c>
       <c r="I2" s="1">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1">
         <v>11</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1">
-        <v>80</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1">
-        <v>4</v>
-      </c>
-      <c r="P2" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1">
-        <v>0</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0</v>
-      </c>
-      <c r="T2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="1">
         <v>10</v>
       </c>
@@ -1762,53 +1647,23 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="6">
-        <v>-1</v>
+      <c r="F3" s="1">
+        <v>3</v>
       </c>
       <c r="G3" s="1">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1">
         <v>3</v>
       </c>
-      <c r="H3" s="1">
-        <v>15</v>
-      </c>
       <c r="I3" s="1">
-        <v>3</v>
-      </c>
-      <c r="J3" s="1">
         <v>11</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="1">
-        <v>80</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
-        <v>4</v>
-      </c>
-      <c r="P3" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1">
-        <v>0</v>
-      </c>
-      <c r="S3" s="1">
-        <v>0</v>
-      </c>
-      <c r="T3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:20">
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:10">
       <c r="A4" s="1">
         <v>20</v>
       </c>
@@ -1824,53 +1679,23 @@
       <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="6">
-        <v>-1</v>
+      <c r="F4" s="1">
+        <v>3</v>
       </c>
       <c r="G4" s="1">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="1">
-        <v>15</v>
-      </c>
       <c r="I4" s="1">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1">
         <v>11</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="1">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1">
-        <v>4</v>
-      </c>
-      <c r="P4" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1">
-        <v>0</v>
-      </c>
-      <c r="T4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:20">
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="1">
         <v>30</v>
       </c>
@@ -1886,53 +1711,23 @@
       <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="6">
-        <v>-1</v>
+      <c r="F5" s="1">
+        <v>3</v>
       </c>
       <c r="G5" s="1">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="1">
-        <v>15</v>
-      </c>
       <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1">
         <v>11</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="1">
-        <v>80</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>4</v>
-      </c>
-      <c r="P5" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:20">
+      <c r="J5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:10">
       <c r="A6" s="1">
         <v>40</v>
       </c>
@@ -1948,53 +1743,23 @@
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="6">
-        <v>-1</v>
+      <c r="F6" s="1">
+        <v>3</v>
       </c>
       <c r="G6" s="1">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" s="1">
-        <v>15</v>
-      </c>
       <c r="I6" s="1">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1">
         <v>11</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="1">
-        <v>80</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>4</v>
-      </c>
-      <c r="P6" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:20">
+      <c r="J6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:10">
       <c r="A7" s="1">
         <v>50</v>
       </c>
@@ -2010,53 +1775,23 @@
       <c r="E7" s="1">
         <v>8</v>
       </c>
-      <c r="F7" s="6">
-        <v>-1</v>
+      <c r="F7" s="1">
+        <v>3</v>
       </c>
       <c r="G7" s="1">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="1">
-        <v>3</v>
-      </c>
-      <c r="J7" s="1">
-        <v>11</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="1">
-        <v>80</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>4</v>
-      </c>
-      <c r="P7" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:20">
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:10">
       <c r="A8" s="1">
         <v>60</v>
       </c>
@@ -2072,53 +1807,23 @@
       <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="6">
-        <v>-1</v>
+      <c r="F8" s="1">
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
-      </c>
-      <c r="J8" s="1">
         <v>16</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="1">
-        <v>80</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>4</v>
-      </c>
-      <c r="P8" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:20">
+      <c r="J8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:10">
       <c r="A9" s="1">
         <v>70</v>
       </c>
@@ -2134,53 +1839,23 @@
       <c r="E9" s="1">
         <v>12</v>
       </c>
-      <c r="F9" s="6">
-        <v>-1</v>
+      <c r="F9" s="1">
+        <v>3</v>
       </c>
       <c r="G9" s="1">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1">
         <v>3</v>
       </c>
-      <c r="H9" s="1">
-        <v>15</v>
-      </c>
       <c r="I9" s="1">
-        <v>3</v>
-      </c>
-      <c r="J9" s="1">
         <v>11</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="1">
-        <v>80</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>4</v>
-      </c>
-      <c r="P9" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:20">
+      <c r="J9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:10">
       <c r="A10" s="1">
         <v>80</v>
       </c>
@@ -2196,53 +1871,23 @@
       <c r="E10" s="1">
         <v>14</v>
       </c>
-      <c r="F10" s="6">
-        <v>-1</v>
+      <c r="F10" s="1">
+        <v>3</v>
       </c>
       <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="H10" s="1">
-        <v>15</v>
-      </c>
       <c r="I10" s="1">
-        <v>3</v>
-      </c>
-      <c r="J10" s="1">
         <v>11</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="1">
-        <v>80</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>4</v>
-      </c>
-      <c r="P10" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:20">
+      <c r="J10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:10">
       <c r="A11" s="1">
         <v>90</v>
       </c>
@@ -2258,50 +1903,20 @@
       <c r="E11" s="1">
         <v>16</v>
       </c>
-      <c r="F11" s="6">
-        <v>-1</v>
+      <c r="F11" s="1">
+        <v>3</v>
       </c>
       <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="1">
-        <v>15</v>
-      </c>
       <c r="I11" s="1">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1">
         <v>11</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="1">
-        <v>80</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>4</v>
-      </c>
-      <c r="P11" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
+      <c r="J11" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2325,25 +1940,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -2439,7 +2054,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2447,29 +2062,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2508,14 +2123,14 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -2546,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2562,270 +2177,266 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D4,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Random</v>
       </c>
       <c r="F4" s="1">
         <v>100</v>
       </c>
       <c r="G4" s="1">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D5,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Random</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
       </c>
       <c r="G5" s="1">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="E6" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D6,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Group</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
       </c>
       <c r="G6" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="E7" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D7,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Group</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
       </c>
       <c r="G7" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7">
-        <v>1032</v>
+      <c r="I7" s="1">
+        <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D8,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Group</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
       </c>
       <c r="G8" s="1">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D9,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Group</v>
       </c>
       <c r="F9" s="1">
         <v>100</v>
       </c>
       <c r="G9" s="1">
-        <v>1042</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>1042</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="E10" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D10,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Group</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>
       </c>
       <c r="G10" s="1">
-        <v>1051</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>1051</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -2838,86 +2449,86 @@
         <v>100</v>
       </c>
       <c r="G11" s="1">
-        <v>1052</v>
+        <v>2041</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>1052</v>
+        <v>2041</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B12" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D12,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Battle</v>
       </c>
       <c r="F12" s="1">
         <v>100</v>
       </c>
       <c r="G12" s="1">
-        <v>1101</v>
+        <v>2042</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>1101</v>
+        <v>2042</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B13" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D13,Define!I:I))</f>
-        <v>SelectActor</v>
+        <v>Resource</v>
       </c>
       <c r="F13" s="1">
         <v>100</v>
       </c>
       <c r="G13" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -2925,9 +2536,7 @@
       <c r="J13" s="1">
         <v>0</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
@@ -2936,17 +2545,17 @@
         <v>2</v>
       </c>
       <c r="B14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D14,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Alcana</v>
       </c>
       <c r="F14" s="1">
         <v>100</v>
@@ -2955,7 +2564,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2964,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2974,34 +2583,36 @@
         <v>2</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D15,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
@@ -3010,34 +2621,36 @@
         <v>2</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D16,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>2102</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>2102</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
@@ -3046,26 +2659,26 @@
         <v>2</v>
       </c>
       <c r="B17" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D17,Define!I:I))</f>
-        <v>Group</v>
+        <v>SelectActor</v>
       </c>
       <c r="F17" s="1">
         <v>100</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -3074,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3084,26 +2697,26 @@
         <v>2</v>
       </c>
       <c r="B18" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="1">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D18,Define!I:I))</f>
-        <v>Group</v>
+        <v>Alcana</v>
       </c>
       <c r="F18" s="1">
         <v>100</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -3112,33 +2725,33 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>203</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D19,Define!I:I))</f>
-        <v>Group</v>
+        <v>Battle</v>
       </c>
       <c r="F19" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -3150,33 +2763,33 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
       </c>
       <c r="D20" s="1">
-        <v>204</v>
+        <v>6</v>
       </c>
       <c r="E20" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D20,Define!I:I))</f>
-        <v>Group</v>
+        <v>Resource</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -3188,33 +2801,33 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="E21" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D21,Define!I:I))</f>
-        <v>Group</v>
+        <v>Resource</v>
       </c>
       <c r="F21" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -3226,109 +2839,107 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D22,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Resource</v>
       </c>
       <c r="F22" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>2041</v>
+        <v>30</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>2041</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E23" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D23,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Random</v>
       </c>
       <c r="F23" s="1">
         <v>100</v>
       </c>
       <c r="G23" s="1">
-        <v>2042</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
       <c r="I23" s="1">
-        <v>2042</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>2</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E24" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D24,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Random</v>
       </c>
       <c r="F24" s="1">
         <v>100</v>
       </c>
       <c r="G24" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -3345,29 +2956,29 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
+        <v>3</v>
+      </c>
+      <c r="B25" s="1">
         <v>2</v>
       </c>
-      <c r="B25" s="1">
-        <v>5</v>
-      </c>
       <c r="C25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D25,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Random</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -3375,113 +2986,109 @@
       <c r="J25" s="1">
         <v>0</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1">
         <v>2</v>
       </c>
-      <c r="B26" s="1">
-        <v>6</v>
-      </c>
       <c r="C26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D26,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Random</v>
       </c>
       <c r="F26" s="1">
         <v>100</v>
       </c>
       <c r="G26" s="1">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
         <v>0</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="B27" s="1">
-        <v>6</v>
-      </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D27,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Shop</v>
       </c>
       <c r="F27" s="1">
         <v>100</v>
       </c>
       <c r="G27" s="1">
-        <v>2102</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>2102</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E28" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D28,Define!I:I))</f>
-        <v>SelectActor</v>
+        <v>Random</v>
       </c>
       <c r="F28" s="1">
         <v>100</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
@@ -3489,37 +3096,35 @@
       <c r="J28" s="1">
         <v>0</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E29" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D29,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Random</v>
       </c>
       <c r="F29" s="1">
         <v>100</v>
       </c>
       <c r="G29" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3527,9 +3132,7 @@
       <c r="J29" s="1">
         <v>0</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
@@ -3538,7 +3141,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
@@ -3551,22 +3154,22 @@
         <v>Battle</v>
       </c>
       <c r="F30" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G30" s="1">
-        <v>-1</v>
+        <v>3041</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
       </c>
       <c r="I30" s="1">
-        <v>0</v>
+        <v>3041</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3576,35 +3179,35 @@
         <v>3</v>
       </c>
       <c r="B31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D31,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Battle</v>
       </c>
       <c r="F31" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G31" s="1">
-        <v>10</v>
+        <v>3042</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3614,7 +3217,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
@@ -3627,10 +3230,10 @@
         <v>Resource</v>
       </c>
       <c r="F32" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="G32" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -3641,9 +3244,7 @@
       <c r="J32" s="1">
         <v>0</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
     </row>
@@ -3652,26 +3253,26 @@
         <v>3</v>
       </c>
       <c r="B33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D33,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Alcana</v>
       </c>
       <c r="F33" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G33" s="1">
-        <v>30</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3680,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3690,34 +3291,36 @@
         <v>3</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D34,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
@@ -3726,34 +3329,36 @@
         <v>3</v>
       </c>
       <c r="B35" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D35,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F35" s="1">
         <v>100</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>3102</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>0</v>
+        <v>3102</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
@@ -3762,17 +3367,17 @@
         <v>3</v>
       </c>
       <c r="B36" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E36" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D36,Define!I:I))</f>
-        <v>Random</v>
+        <v>SelectActor</v>
       </c>
       <c r="F36" s="1">
         <v>100</v>
@@ -3781,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3789,7 +3394,9 @@
       <c r="J36" s="1">
         <v>0</v>
       </c>
-      <c r="K36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
     </row>
@@ -3798,26 +3405,26 @@
         <v>3</v>
       </c>
       <c r="B37" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
       </c>
       <c r="D37" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E37" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D37,Define!I:I))</f>
-        <v>Random</v>
+        <v>Alcana</v>
       </c>
       <c r="F37" s="1">
         <v>100</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3825,29 +3432,30 @@
       <c r="J37" s="1">
         <v>0</v>
       </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E38" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D38,Define!I:I))</f>
-        <v>Shop</v>
+        <v>Battle</v>
       </c>
       <c r="F38" s="1">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G38" s="1">
         <v>-1</v>
@@ -3862,33 +3470,33 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" s="1">
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E39" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D39,Define!I:I))</f>
-        <v>Random</v>
+        <v>Resource</v>
       </c>
       <c r="F39" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3899,32 +3507,34 @@
       <c r="J39" s="1">
         <v>0</v>
       </c>
-      <c r="K39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="1">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D40,Define!I:I))</f>
-        <v>Random</v>
+        <v>Resource</v>
       </c>
       <c r="F40" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -3935,108 +3545,108 @@
       <c r="J40" s="1">
         <v>0</v>
       </c>
-      <c r="K40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C41" s="1">
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E41" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D41,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Resource</v>
       </c>
       <c r="F41" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G41" s="1">
-        <v>3041</v>
+        <v>40</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
       </c>
       <c r="I41" s="1">
-        <v>3041</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E42" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D42,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Random</v>
       </c>
       <c r="F42" s="1">
         <v>100</v>
       </c>
       <c r="G42" s="1">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>2</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="1">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E43" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D43,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Random</v>
       </c>
       <c r="F43" s="1">
         <v>100</v>
       </c>
       <c r="G43" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4053,29 +3663,29 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E44" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D44,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Random</v>
       </c>
       <c r="F44" s="1">
         <v>100</v>
       </c>
       <c r="G44" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
@@ -4083,104 +3693,100 @@
       <c r="J44" s="1">
         <v>0</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E45" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D45,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Random</v>
       </c>
       <c r="F45" s="1">
         <v>100</v>
       </c>
       <c r="G45" s="1">
-        <v>3101</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>3101</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B46" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E46" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D46,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Shop</v>
       </c>
       <c r="F46" s="1">
         <v>100</v>
       </c>
       <c r="G46" s="1">
-        <v>3102</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
       </c>
       <c r="I46" s="1">
-        <v>3102</v>
+        <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1">
         <v>3</v>
       </c>
-      <c r="B47" s="1">
-        <v>7</v>
-      </c>
       <c r="C47" s="1">
         <v>0</v>
       </c>
       <c r="D47" s="1">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E47" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D47,Define!I:I))</f>
-        <v>SelectActor</v>
+        <v>Random</v>
       </c>
       <c r="F47" s="1">
         <v>100</v>
@@ -4189,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
@@ -4197,37 +3803,35 @@
       <c r="J47" s="1">
         <v>0</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1">
         <v>3</v>
       </c>
-      <c r="B48" s="1">
-        <v>7</v>
-      </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E48" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D48,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Random</v>
       </c>
       <c r="F48" s="1">
         <v>100</v>
       </c>
       <c r="G48" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
@@ -4235,9 +3839,8 @@
       <c r="J48" s="1">
         <v>0</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
       <c r="M48" s="1"/>
     </row>
     <row r="49" spans="1:13">
@@ -4245,7 +3848,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -4258,22 +3861,22 @@
         <v>Battle</v>
       </c>
       <c r="F49" s="1">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G49" s="1">
-        <v>-1</v>
+        <v>4041</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
       </c>
       <c r="I49" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -4283,35 +3886,35 @@
         <v>4</v>
       </c>
       <c r="B50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D50,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Battle</v>
       </c>
       <c r="F50" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G50" s="1">
-        <v>20</v>
+        <v>4042</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>0</v>
+        <v>4042</v>
       </c>
       <c r="J50" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -4321,7 +3924,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1">
         <v>0</v>
@@ -4334,10 +3937,10 @@
         <v>Resource</v>
       </c>
       <c r="F51" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G51" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -4348,9 +3951,7 @@
       <c r="J51" s="1">
         <v>0</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
     </row>
@@ -4359,26 +3960,26 @@
         <v>4</v>
       </c>
       <c r="B52" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E52" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D52,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Alcana</v>
       </c>
       <c r="F52" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G52" s="1">
-        <v>40</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4387,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -4397,34 +3998,36 @@
         <v>4</v>
       </c>
       <c r="B53" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C53" s="1">
         <v>0</v>
       </c>
       <c r="D53" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D53,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F53" s="1">
         <v>100</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
       </c>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
     </row>
@@ -4433,34 +4036,36 @@
         <v>4</v>
       </c>
       <c r="B54" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D54,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F54" s="1">
         <v>100</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>4102</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <v>0</v>
+        <v>4102</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
-      </c>
-      <c r="K54" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
     </row>
@@ -4469,17 +4074,17 @@
         <v>4</v>
       </c>
       <c r="B55" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1">
         <v>0</v>
       </c>
       <c r="D55" s="1">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D55,Define!I:I))</f>
-        <v>Random</v>
+        <v>SelectActor</v>
       </c>
       <c r="F55" s="1">
         <v>100</v>
@@ -4488,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -4496,7 +4101,9 @@
       <c r="J55" s="1">
         <v>0</v>
       </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
     </row>
@@ -4505,26 +4112,26 @@
         <v>4</v>
       </c>
       <c r="B56" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
       </c>
       <c r="D56" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D56,Define!I:I))</f>
-        <v>Random</v>
+        <v>Alcana</v>
       </c>
       <c r="F56" s="1">
         <v>100</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -4532,29 +4139,31 @@
       <c r="J56" s="1">
         <v>0</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E57" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D57,Define!I:I))</f>
-        <v>Shop</v>
+        <v>Battle</v>
       </c>
       <c r="F57" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G57" s="1">
         <v>-1</v>
@@ -4569,30 +4178,30 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
       </c>
       <c r="D58" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E58" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D58,Define!I:I))</f>
-        <v>Random</v>
+        <v>Actor</v>
       </c>
       <c r="F58" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -4606,29 +4215,31 @@
       <c r="J58" s="1">
         <v>0</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B59" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E59" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D59,Define!I:I))</f>
-        <v>Random</v>
+        <v>SelectActor</v>
       </c>
       <c r="F59" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -4636,98 +4247,100 @@
       <c r="H59" s="1">
         <v>0</v>
       </c>
-      <c r="I59" s="1">
-        <v>0</v>
+      <c r="I59">
+        <v>252</v>
       </c>
       <c r="J59" s="1">
         <v>0</v>
       </c>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B60" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D60,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Resource</v>
       </c>
       <c r="F60" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
-        <v>4041</v>
+        <v>20</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="J60" s="1">
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E61" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D61,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Resource</v>
       </c>
       <c r="F61" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G61" s="1">
-        <v>4042</v>
+        <v>30</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
       </c>
       <c r="I61" s="1">
-        <v>4042</v>
+        <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B62" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -4740,7 +4353,7 @@
         <v>Resource</v>
       </c>
       <c r="F62" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G62" s="1">
         <v>40</v>
@@ -4754,35 +4367,37 @@
       <c r="J62" s="1">
         <v>0</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B63" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E63" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D63,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Random</v>
       </c>
       <c r="F63" s="1">
         <v>100</v>
       </c>
       <c r="G63" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -4790,104 +4405,98 @@
       <c r="J63" s="1">
         <v>0</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E64" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D64,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Random</v>
       </c>
       <c r="F64" s="1">
         <v>100</v>
       </c>
       <c r="G64" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
       </c>
       <c r="I64" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="J64" s="1">
         <v>0</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E65" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D65,Define!I:I))</f>
-        <v>Boss</v>
+        <v>Random</v>
       </c>
       <c r="F65" s="1">
         <v>100</v>
       </c>
       <c r="G65" s="1">
-        <v>4102</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>4102</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>2</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B66" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" s="1">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E66" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D66,Define!I:I))</f>
-        <v>SelectActor</v>
+        <v>Random</v>
       </c>
       <c r="F66" s="1">
         <v>100</v>
@@ -4896,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
@@ -4904,28 +4513,26 @@
       <c r="J66" s="1">
         <v>0</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B67" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E67" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D67,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Shop</v>
       </c>
       <c r="F67" s="1">
         <v>100</v>
@@ -4934,7 +4541,7 @@
         <v>-1</v>
       </c>
       <c r="H67" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -4943,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -4953,23 +4560,23 @@
         <v>5</v>
       </c>
       <c r="B68" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E68" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D68,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Random</v>
       </c>
       <c r="F68" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G68" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -4980,9 +4587,7 @@
       <c r="J68" s="1">
         <v>0</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
@@ -4991,20 +4596,20 @@
         <v>5</v>
       </c>
       <c r="B69" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="E69" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D69,Define!I:I))</f>
-        <v>Actor</v>
+        <v>Random</v>
       </c>
       <c r="F69" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -5018,9 +4623,7 @@
       <c r="J69" s="1">
         <v>0</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
     </row>
@@ -5029,35 +4632,35 @@
         <v>5</v>
       </c>
       <c r="B70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
       </c>
       <c r="D70" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E70" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D70,Define!I:I))</f>
-        <v>SelectActor</v>
+        <v>Battle</v>
       </c>
       <c r="F70" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>5041</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
       </c>
-      <c r="I70">
-        <v>252</v>
+      <c r="I70" s="1">
+        <v>5041</v>
       </c>
       <c r="J70" s="1">
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -5067,35 +4670,35 @@
         <v>5</v>
       </c>
       <c r="B71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E71" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D71,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Battle</v>
       </c>
       <c r="F71" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G71" s="1">
-        <v>20</v>
+        <v>5042</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="J71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -5105,7 +4708,7 @@
         <v>5</v>
       </c>
       <c r="B72" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
@@ -5118,10 +4721,10 @@
         <v>Resource</v>
       </c>
       <c r="F72" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G72" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -5132,9 +4735,7 @@
       <c r="J72" s="1">
         <v>0</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
     </row>
@@ -5143,26 +4744,26 @@
         <v>5</v>
       </c>
       <c r="B73" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D73,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Alcana</v>
       </c>
       <c r="F73" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G73" s="1">
-        <v>40</v>
+        <v>-1</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
@@ -5171,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -5181,34 +4782,36 @@
         <v>5</v>
       </c>
       <c r="B74" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C74" s="1">
         <v>0</v>
       </c>
       <c r="D74" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D74,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F74" s="1">
         <v>100</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>5101</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
       </c>
       <c r="I74" s="1">
-        <v>0</v>
+        <v>5101</v>
       </c>
       <c r="J74" s="1">
         <v>0</v>
       </c>
-      <c r="K74" s="1"/>
+      <c r="K74" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
     </row>
@@ -5217,62 +4820,64 @@
         <v>5</v>
       </c>
       <c r="B75" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
       </c>
       <c r="D75" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D75,Define!I:I))</f>
-        <v>Random</v>
+        <v>Boss</v>
       </c>
       <c r="F75" s="1">
         <v>100</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
       </c>
       <c r="I75" s="1">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="J75" s="1">
-        <v>0</v>
-      </c>
-      <c r="K75" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:11">
       <c r="A76" s="1">
         <v>5</v>
       </c>
       <c r="B76" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1">
         <v>0</v>
       </c>
       <c r="D76" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D76,Define!I:I))</f>
-        <v>Random</v>
+        <v>Alcana</v>
       </c>
       <c r="F76" s="1">
         <v>100</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
@@ -5280,35 +4885,35 @@
       <c r="J76" s="1">
         <v>0</v>
       </c>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
+      <c r="K76" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="1">
         <v>5</v>
       </c>
       <c r="B77" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D77,Define!I:I))</f>
-        <v>Random</v>
+        <v>Alcana</v>
       </c>
       <c r="F77" s="1">
         <v>100</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
@@ -5316,32 +4921,34 @@
       <c r="J77" s="1">
         <v>0</v>
       </c>
-      <c r="K77" s="1"/>
+      <c r="K77" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:11">
       <c r="A78" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D78,Define!I:I))</f>
-        <v>Shop</v>
+        <v>SelectActor</v>
       </c>
       <c r="F78" s="1">
         <v>100</v>
       </c>
       <c r="G78" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -5353,33 +4960,31 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-    </row>
-    <row r="79" spans="1:13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" s="1">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E79" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D79,Define!I:I))</f>
-        <v>Random</v>
+        <v>Shop</v>
       </c>
       <c r="F79" s="1">
         <v>100</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -5390,55 +4995,55 @@
       <c r="J79" s="1">
         <v>0</v>
       </c>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="K79" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E80" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D80,Define!I:I))</f>
-        <v>Random</v>
+        <v>Battle</v>
       </c>
       <c r="F80" s="1">
         <v>100</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>6021</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
       </c>
       <c r="I80" s="1">
-        <v>0</v>
+        <v>6021</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
       </c>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="K80" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B81" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
@@ -5451,32 +5056,30 @@
         <v>100</v>
       </c>
       <c r="G81" s="1">
-        <v>5041</v>
+        <v>6022</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
       </c>
       <c r="I81" s="1">
-        <v>5041</v>
+        <v>6022</v>
       </c>
       <c r="J81" s="1">
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-    </row>
-    <row r="82" spans="1:13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B82" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
@@ -5488,462 +5091,56 @@
       <c r="F82" s="1">
         <v>100</v>
       </c>
-      <c r="G82" s="1">
-        <v>5042</v>
+      <c r="G82">
+        <v>6031</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
       </c>
-      <c r="I82" s="1">
-        <v>5042</v>
-      </c>
-      <c r="J82" s="1">
+      <c r="I82">
+        <v>6031</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="1">
+        <v>6</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0</v>
+      </c>
+      <c r="D83" s="1">
         <v>2</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-    </row>
-    <row r="83" spans="1:13">
-      <c r="A83" s="1">
-        <v>5</v>
-      </c>
-      <c r="B83" s="1">
-        <v>5</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0</v>
-      </c>
-      <c r="D83" s="1">
-        <v>6</v>
       </c>
       <c r="E83" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D83,Define!I:I))</f>
-        <v>Resource</v>
+        <v>Boss</v>
       </c>
       <c r="F83" s="1">
         <v>100</v>
       </c>
       <c r="G83" s="1">
-        <v>50</v>
+        <v>6101</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
       </c>
       <c r="I83" s="1">
-        <v>0</v>
+        <v>6101</v>
       </c>
       <c r="J83" s="1">
         <v>0</v>
       </c>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-      <c r="M83" s="1"/>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="1">
-        <v>5</v>
-      </c>
-      <c r="B84" s="1">
-        <v>5</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="1">
-        <v>4</v>
-      </c>
-      <c r="E84" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D84,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F84" s="1">
-        <v>100</v>
-      </c>
-      <c r="G84" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H84" s="1">
-        <v>20</v>
-      </c>
-      <c r="I84" s="1">
-        <v>0</v>
-      </c>
-      <c r="J84" s="1">
-        <v>0</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L84" s="1"/>
-      <c r="M84" s="1"/>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="1">
-        <v>5</v>
-      </c>
-      <c r="B85" s="1">
-        <v>6</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0</v>
-      </c>
-      <c r="D85" s="1">
-        <v>2</v>
-      </c>
-      <c r="E85" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D85,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F85" s="1">
-        <v>100</v>
-      </c>
-      <c r="G85" s="1">
-        <v>5101</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0</v>
-      </c>
-      <c r="I85" s="1">
-        <v>5101</v>
-      </c>
-      <c r="J85" s="1">
-        <v>0</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L85" s="1"/>
-      <c r="M85" s="1"/>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="1">
-        <v>5</v>
-      </c>
-      <c r="B86" s="1">
-        <v>6</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="1">
-        <v>2</v>
-      </c>
-      <c r="E86" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D86,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F86" s="1">
-        <v>100</v>
-      </c>
-      <c r="G86" s="1">
-        <v>5102</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1">
-        <v>5102</v>
-      </c>
-      <c r="J86" s="1">
-        <v>2</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="1">
-        <v>5</v>
-      </c>
-      <c r="B87" s="1">
-        <v>7</v>
-      </c>
-      <c r="C87" s="1">
-        <v>0</v>
-      </c>
-      <c r="D87" s="1">
-        <v>4</v>
-      </c>
-      <c r="E87" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D87,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F87" s="1">
-        <v>100</v>
-      </c>
-      <c r="G87" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H87" s="1">
-        <v>20</v>
-      </c>
-      <c r="I87" s="1">
-        <v>0</v>
-      </c>
-      <c r="J87" s="1">
-        <v>0</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="1">
-        <v>5</v>
-      </c>
-      <c r="B88" s="1">
-        <v>7</v>
-      </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="1">
-        <v>4</v>
-      </c>
-      <c r="E88" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D88,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F88" s="1">
-        <v>100</v>
-      </c>
-      <c r="G88" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H88" s="1">
-        <v>210</v>
-      </c>
-      <c r="I88" s="1">
-        <v>0</v>
-      </c>
-      <c r="J88" s="1">
-        <v>0</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="1">
-        <v>6</v>
-      </c>
-      <c r="B89" s="1">
-        <v>1</v>
-      </c>
-      <c r="C89" s="1">
-        <v>0</v>
-      </c>
-      <c r="D89" s="1">
-        <v>8</v>
-      </c>
-      <c r="E89" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D89,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F89" s="1">
-        <v>100</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0</v>
-      </c>
-      <c r="H89" s="1">
-        <v>0</v>
-      </c>
-      <c r="I89" s="1">
-        <v>0</v>
-      </c>
-      <c r="J89" s="1">
-        <v>0</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="1">
-        <v>6</v>
-      </c>
-      <c r="B90" s="1">
-        <v>1</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1">
-        <v>9</v>
-      </c>
-      <c r="E90" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D90,Define!I:I))</f>
-        <v>Shop</v>
-      </c>
-      <c r="F90" s="1">
-        <v>100</v>
-      </c>
-      <c r="G90" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H90" s="1">
-        <v>0</v>
-      </c>
-      <c r="I90" s="1">
-        <v>0</v>
-      </c>
-      <c r="J90" s="1">
-        <v>0</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="1">
-        <v>6</v>
-      </c>
-      <c r="B91" s="1">
-        <v>2</v>
-      </c>
-      <c r="C91" s="1">
-        <v>0</v>
-      </c>
-      <c r="D91" s="1">
-        <v>1</v>
-      </c>
-      <c r="E91" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D91,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F91" s="1">
-        <v>100</v>
-      </c>
-      <c r="G91" s="1">
-        <v>6021</v>
-      </c>
-      <c r="H91" s="1">
-        <v>0</v>
-      </c>
-      <c r="I91" s="1">
-        <v>6021</v>
-      </c>
-      <c r="J91" s="1">
-        <v>0</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="1">
-        <v>6</v>
-      </c>
-      <c r="B92" s="1">
-        <v>2</v>
-      </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1">
-        <v>1</v>
-      </c>
-      <c r="E92" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D92,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F92" s="1">
-        <v>100</v>
-      </c>
-      <c r="G92" s="1">
-        <v>6022</v>
-      </c>
-      <c r="H92" s="1">
-        <v>0</v>
-      </c>
-      <c r="I92" s="1">
-        <v>6022</v>
-      </c>
-      <c r="J92" s="1">
-        <v>0</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="1">
-        <v>6</v>
-      </c>
-      <c r="B93" s="1">
-        <v>3</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0</v>
-      </c>
-      <c r="D93" s="1">
-        <v>1</v>
-      </c>
-      <c r="E93" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D93,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F93" s="1">
-        <v>100</v>
-      </c>
-      <c r="G93">
-        <v>6031</v>
-      </c>
-      <c r="H93" s="1">
-        <v>0</v>
-      </c>
-      <c r="I93">
-        <v>6031</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="1">
-        <v>6</v>
-      </c>
-      <c r="B94" s="1">
-        <v>4</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0</v>
-      </c>
-      <c r="D94" s="1">
-        <v>2</v>
-      </c>
-      <c r="E94" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D94,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F94" s="1">
-        <v>100</v>
-      </c>
-      <c r="G94" s="1">
-        <v>6101</v>
-      </c>
-      <c r="H94" s="1">
-        <v>0</v>
-      </c>
-      <c r="I94" s="1">
-        <v>6101</v>
-      </c>
-      <c r="J94" s="1">
-        <v>0</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>66</v>
+      <c r="K83" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5960,25 +5157,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6458,25 +5655,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6500,10 +5697,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:3">
@@ -6511,10 +5708,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="39" spans="1:4">
@@ -6522,10 +5719,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -6534,10 +5731,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -6546,10 +5743,10 @@
         <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -6558,10 +5755,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -6570,10 +5767,10 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -6582,10 +5779,10 @@
         <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -6594,10 +5791,10 @@
         <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="39" spans="1:3">
@@ -6605,10 +5802,10 @@
         <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
@@ -6616,10 +5813,10 @@
         <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
@@ -6627,10 +5824,10 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
@@ -6638,10 +5835,10 @@
         <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6649,10 +5846,10 @@
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6660,10 +5857,10 @@
         <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6671,10 +5868,10 @@
         <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6682,10 +5879,10 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -6705,13 +5902,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:10">
@@ -6719,19 +5916,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -6739,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -6756,19 +5953,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -6776,19 +5973,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -6796,19 +5993,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -6816,19 +6013,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:10">
@@ -6836,19 +6033,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -6856,13 +6053,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -6870,13 +6067,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -6884,13 +6081,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -6898,13 +6095,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -6912,13 +6109,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -6926,7 +6123,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -6934,7 +6131,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -6942,7 +6139,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -6950,7 +6147,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -6958,7 +6155,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -6966,7 +6163,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -6974,7 +6171,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -6982,7 +6179,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -6990,7 +6187,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -6998,7 +6195,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -7006,7 +6203,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -7014,7 +6211,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>NameId</t>
+  </si>
+  <si>
+    <t>StageNo</t>
   </si>
   <si>
     <t>AchieveTextId</t>
@@ -607,9 +610,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -625,6 +628,44 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -633,14 +674,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -654,9 +710,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -664,34 +719,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -707,49 +741,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -762,8 +756,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -789,7 +792,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,7 +834,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -813,31 +870,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,7 +936,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -861,19 +954,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -885,85 +966,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -974,6 +977,33 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1007,17 +1037,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1037,40 +1063,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1082,7 +1085,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1091,7 +1094,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1100,127 +1103,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1559,15 +1562,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
-    <col min="3" max="3" width="8.45454545454546" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="4"/>
-    <col min="10" max="10" width="32" customWidth="1"/>
+    <col min="4" max="4" width="8.45454545454546" customWidth="1"/>
+    <col min="5" max="5" width="10.3636363636364" customWidth="1"/>
+    <col min="6" max="6" width="8.72727272727273" style="4"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,8 +1602,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1607,31 +1614,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
         <v>10001</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
         <v>3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>15</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>3</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1">
         <v>10</v>
       </c>
@@ -1639,31 +1649,34 @@
         <v>10</v>
       </c>
       <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>10001</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>15</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>3</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:11">
       <c r="A4" s="1">
         <v>20</v>
       </c>
@@ -1671,31 +1684,34 @@
         <v>20</v>
       </c>
       <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>10001</v>
       </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
       <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>15</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>3</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>11</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="1">
         <v>30</v>
       </c>
@@ -1703,31 +1719,34 @@
         <v>30</v>
       </c>
       <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
         <v>10001</v>
       </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
       <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>15</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>11</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
+      <c r="K5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="1">
         <v>40</v>
       </c>
@@ -1735,31 +1754,34 @@
         <v>40</v>
       </c>
       <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1">
         <v>10001</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
       <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>15</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>11</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:10">
+      <c r="K6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="1">
         <v>50</v>
       </c>
@@ -1767,31 +1789,34 @@
         <v>50</v>
       </c>
       <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
         <v>10001</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
       <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>8</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>3</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>15</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>3</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:10">
+      <c r="K7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
       <c r="A8" s="1">
         <v>60</v>
       </c>
@@ -1799,31 +1824,34 @@
         <v>60</v>
       </c>
       <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1">
         <v>10001</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
       <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>15</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>16</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
       <c r="A9" s="1">
         <v>70</v>
       </c>
@@ -1831,31 +1859,34 @@
         <v>70</v>
       </c>
       <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
         <v>10001</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
       <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>12</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>15</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>3</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>11</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="K9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:11">
       <c r="A10" s="1">
         <v>80</v>
       </c>
@@ -1863,31 +1894,34 @@
         <v>80</v>
       </c>
       <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
         <v>10001</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
       <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
         <v>14</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>15</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>3</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>11</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:10">
+      <c r="K10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:11">
       <c r="A11" s="1">
         <v>90</v>
       </c>
@@ -1895,28 +1929,31 @@
         <v>90</v>
       </c>
       <c r="C11" s="1">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
         <v>10001</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
       <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
         <v>16</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>15</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>3</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>11</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>19</v>
+      <c r="K11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1940,25 +1977,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -2062,29 +2099,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2123,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2161,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2271,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2309,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2347,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2385,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2423,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2461,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2499,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2573,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2611,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2649,7 +2686,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2687,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2725,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2763,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2801,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2839,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2877,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3059,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3169,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3207,7 +3244,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3281,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3319,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -3357,7 +3394,7 @@
         <v>2</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -3395,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -3433,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M37" s="1"/>
     </row>
@@ -3470,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -3508,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3546,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -3584,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -3766,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3876,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -3914,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -3988,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -4026,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -4064,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -4102,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -4140,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -4178,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4216,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -4254,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -4292,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -4330,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -4368,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -4550,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -4660,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -4698,7 +4735,7 @@
         <v>2</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -4772,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -4810,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
@@ -4848,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -4886,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -4922,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -4960,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -4996,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -5032,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -5068,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -5104,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -5140,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -5157,25 +5194,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5655,25 +5692,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5697,10 +5734,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:3">
@@ -5708,10 +5745,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="39" spans="1:4">
@@ -5719,10 +5756,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -5731,10 +5768,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -5743,10 +5780,10 @@
         <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -5755,10 +5792,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -5767,10 +5804,10 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -5779,10 +5816,10 @@
         <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -5791,10 +5828,10 @@
         <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="39" spans="1:3">
@@ -5802,10 +5839,10 @@
         <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
@@ -5813,10 +5850,10 @@
         <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
@@ -5824,10 +5861,10 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
@@ -5835,10 +5872,10 @@
         <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5846,10 +5883,10 @@
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5857,10 +5894,10 @@
         <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5868,10 +5905,10 @@
         <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5879,10 +5916,10 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5902,13 +5939,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:10">
@@ -5916,19 +5953,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -5936,13 +5973,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -5953,19 +5990,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -5973,19 +6010,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -5993,19 +6030,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -6013,19 +6050,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:10">
@@ -6033,19 +6070,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -6053,13 +6090,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -6067,13 +6104,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -6081,13 +6118,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -6095,13 +6132,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -6109,13 +6146,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -6123,7 +6160,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -6131,7 +6168,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -6139,7 +6176,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -6147,7 +6184,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -6155,7 +6192,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -6163,7 +6200,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -6171,7 +6208,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -6179,7 +6216,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -6187,7 +6224,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -6195,7 +6232,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -6203,7 +6240,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -6211,7 +6248,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -517,7 +517,7 @@
     <t>隷従属度フラグを管理</t>
   </si>
   <si>
-    <t>Recover</t>
+    <t>Event</t>
   </si>
   <si>
     <t>神化した後</t>
@@ -609,10 +609,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -628,6 +628,96 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -636,6 +726,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -652,105 +750,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -766,7 +766,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -792,7 +792,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,133 +852,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -948,7 +876,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -960,7 +918,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -977,33 +977,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1039,11 +1012,42 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1063,17 +1067,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1085,145 +1085,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1965,10 +1965,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="22.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="18.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2000,86 +2000,30 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>INDEX(Define!B:B,MATCH(C2,Define!A:A))</f>
-        <v>Tactics開始</v>
+        <v>Tactics開始(UI表示前)</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>INDEX(Define!E:E,MATCH(E2,Define!D:D))</f>
-        <v>コマンドを制限する</v>
+        <v>ADV再生</v>
       </c>
       <c r="G2" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="str">
-        <f>INDEX(Define!B:B,MATCH(C3,Define!A:A))</f>
-        <v>Tactics開始</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="str">
-        <f>INDEX(Define!E:E,MATCH(E3,Define!D:D))</f>
-        <v>コマンドを制限する</v>
-      </c>
-      <c r="G3" s="1">
-        <v>6</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <f>INDEX(Define!B:B,MATCH(C4,Define!A:A))</f>
-        <v>Tactics開始</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="str">
-        <f>INDEX(Define!E:E,MATCH(E4,Define!D:D))</f>
-        <v>コマンドを制限する</v>
-      </c>
-      <c r="G4" s="1">
-        <v>6</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -609,10 +609,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -628,8 +628,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -642,16 +643,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -673,8 +680,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -688,7 +696,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -726,18 +741,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -749,13 +757,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -764,9 +765,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -786,13 +786,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,7 +798,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -822,103 +822,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -936,13 +840,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -960,13 +948,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,8 +1012,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1047,6 +1049,15 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -1066,17 +1077,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1085,145 +1085,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1965,8 +1965,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="4" max="4" width="22.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="18.3636363636364" customWidth="1"/>
@@ -2023,6 +2023,34 @@
         <v>10</v>
       </c>
       <c r="H2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>INDEX(Define!B:B,MATCH(C3,Define!A:A))</f>
+        <v>Tactics開始(UI表示前)</v>
+      </c>
+      <c r="E3" s="1">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>INDEX(Define!E:E,MATCH(E3,Define!D:D))</f>
+        <v>ADV再生</v>
+      </c>
+      <c r="G3" s="1">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -609,10 +609,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -630,7 +630,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -650,8 +665,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -659,6 +689,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -680,16 +726,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -702,24 +748,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -727,7 +758,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -738,37 +769,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -786,7 +786,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -798,13 +882,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -816,7 +924,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,145 +966,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -977,6 +977,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -991,6 +1000,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1020,63 +1077,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1085,145 +1085,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2000,7 +2000,7 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="122">
   <si>
     <t>Id</t>
   </si>
@@ -133,52 +133,19 @@
     <t>Seek=0でランダム生成用</t>
   </si>
   <si>
-    <t>火属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>雷属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>氷属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>光属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>闇属性ランダムドロップ</t>
-  </si>
-  <si>
-    <t>中ボス</t>
-  </si>
-  <si>
-    <t>中ボスハード</t>
-  </si>
-  <si>
-    <t>魔法ランダムランク10</t>
+    <t>バトル</t>
+  </si>
+  <si>
+    <t>魔法入手</t>
+  </si>
+  <si>
+    <t>シイナ加入</t>
+  </si>
+  <si>
+    <t>バトル(ハード)</t>
   </si>
   <si>
     <t>ボス戦</t>
-  </si>
-  <si>
-    <t>仲間選択 3人までランダム</t>
-  </si>
-  <si>
-    <t>レリック</t>
-  </si>
-  <si>
-    <t>ショップ</t>
-  </si>
-  <si>
-    <t>ボス戦ハード</t>
-  </si>
-  <si>
-    <t>魔法ランダムランク20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仲間自由選択 </t>
-  </si>
-  <si>
-    <t>ボス</t>
   </si>
   <si>
     <t>GroupId</t>
@@ -609,10 +576,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -628,24 +595,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -665,11 +616,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -680,8 +638,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -689,6 +648,53 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -704,55 +710,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -765,10 +725,17 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -786,7 +753,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -798,97 +915,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -900,73 +933,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -983,8 +950,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1000,54 +967,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1077,6 +996,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1085,145 +1052,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2125,7 +2092,7 @@
       <c r="H2" s="1">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>113</v>
       </c>
       <c r="J2" s="1">
@@ -2139,7 +2106,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -2177,7 +2144,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2186,17 +2153,17 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D4,Define!I:I))</f>
-        <v>Random</v>
+        <v>Battle</v>
       </c>
       <c r="F4" s="1">
         <v>100</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -2207,68 +2174,72 @@
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D5,Define!I:I))</f>
-        <v>Random</v>
+        <v>Alcana</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D6,Define!I:I))</f>
-        <v>Group</v>
+        <v>Battle</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -2287,64 +2258,64 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D7,Define!I:I))</f>
-        <v>Group</v>
+        <v>Event</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>203</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D8,Define!I:I))</f>
-        <v>Group</v>
+        <v>Battle</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -2356,33 +2327,33 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D9,Define!I:I))</f>
-        <v>Group</v>
+        <v>Battle</v>
       </c>
       <c r="F9" s="1">
         <v>100</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2394,33 +2365,33 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>205</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D10,Define!I:I))</f>
-        <v>Group</v>
+        <v>Battle</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -2429,2728 +2400,1116 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
         <v>2</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D11,Define!I:I))</f>
-        <v>Battle</v>
+        <v>Boss</v>
       </c>
       <c r="F11" s="1">
         <v>100</v>
       </c>
       <c r="G11" s="1">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="1">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D12,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F12" s="1">
-        <v>100</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2042</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2042</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="1">
-        <v>2</v>
-      </c>
-      <c r="B13" s="1">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D13,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F13" s="1">
-        <v>100</v>
-      </c>
-      <c r="G13" s="1">
-        <v>15</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="1">
-        <v>2</v>
-      </c>
-      <c r="B14" s="1">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D14,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F14" s="1">
-        <v>100</v>
-      </c>
-      <c r="G14" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>10</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="1">
-        <v>2</v>
-      </c>
-      <c r="B15" s="1">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D15,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F15" s="1">
-        <v>100</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2101</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>2101</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="1">
-        <v>2</v>
-      </c>
-      <c r="B16" s="1">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D16,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F16" s="1">
-        <v>100</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2102</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>2102</v>
-      </c>
-      <c r="J16" s="1">
-        <v>2</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="1">
-        <v>2</v>
-      </c>
-      <c r="B17" s="1">
-        <v>7</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>8</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D17,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F17" s="1">
-        <v>100</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4</v>
-      </c>
-      <c r="H17" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="1">
-        <v>2</v>
-      </c>
-      <c r="B18" s="1">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D18,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F18" s="1">
-        <v>100</v>
-      </c>
-      <c r="G18" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>200</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="1">
-        <v>3</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D19,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F19" s="1">
-        <v>90</v>
-      </c>
-      <c r="G19" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>6</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D20,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5</v>
-      </c>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="1">
-        <v>3</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>6</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D21,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="G21" s="1">
-        <v>20</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="1">
-        <v>3</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D22,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="1">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D23,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F23" s="1">
-        <v>100</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="1">
-        <v>3</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D24,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F24" s="1">
-        <v>100</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="1">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D25,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F25" s="1">
-        <v>100</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="1">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D26,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F26" s="1">
-        <v>100</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="1">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>9</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D27,Define!I:I))</f>
-        <v>Shop</v>
-      </c>
-      <c r="F27" s="1">
-        <v>100</v>
-      </c>
-      <c r="G27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="1">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1">
-        <v>3</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D28,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F28" s="1">
-        <v>100</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="1">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1">
-        <v>3</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D29,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F29" s="1">
-        <v>100</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>0</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="1">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1">
-        <v>4</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D30,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F30" s="1">
-        <v>100</v>
-      </c>
-      <c r="G30" s="1">
-        <v>3041</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>3041</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="1">
-        <v>3</v>
-      </c>
-      <c r="B31" s="1">
-        <v>4</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D31,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F31" s="1">
-        <v>100</v>
-      </c>
-      <c r="G31" s="1">
-        <v>3042</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
-        <v>3042</v>
-      </c>
-      <c r="J31" s="1">
-        <v>2</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="1">
-        <v>3</v>
-      </c>
-      <c r="B32" s="1">
-        <v>5</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>6</v>
-      </c>
-      <c r="E32" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D32,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F32" s="1">
-        <v>100</v>
-      </c>
-      <c r="G32" s="1">
-        <v>25</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="1">
-        <v>3</v>
-      </c>
-      <c r="B33" s="1">
-        <v>5</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D33,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F33" s="1">
-        <v>100</v>
-      </c>
-      <c r="G33" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H33" s="1">
-        <v>10</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="1">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1">
-        <v>6</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D34,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F34" s="1">
-        <v>100</v>
-      </c>
-      <c r="G34" s="1">
-        <v>3101</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>3101</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="1">
-        <v>3</v>
-      </c>
-      <c r="B35" s="1">
-        <v>6</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D35,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F35" s="1">
-        <v>100</v>
-      </c>
-      <c r="G35" s="1">
-        <v>3102</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>3102</v>
-      </c>
-      <c r="J35" s="1">
-        <v>2</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="1">
-        <v>3</v>
-      </c>
-      <c r="B36" s="1">
-        <v>7</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1">
-        <v>8</v>
-      </c>
-      <c r="E36" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D36,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F36" s="1">
-        <v>100</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="1">
-        <v>3</v>
-      </c>
-      <c r="B37" s="1">
-        <v>7</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1">
-        <v>4</v>
-      </c>
-      <c r="E37" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D37,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F37" s="1">
-        <v>100</v>
-      </c>
-      <c r="G37" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H37" s="1">
-        <v>200</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="1">
-        <v>4</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D38,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F38" s="1">
-        <v>93</v>
-      </c>
-      <c r="G38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="1">
-        <v>4</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0</v>
-      </c>
-      <c r="D39" s="1">
-        <v>6</v>
-      </c>
-      <c r="E39" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D39,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F39" s="1">
-        <v>4</v>
-      </c>
-      <c r="G39" s="1">
-        <v>20</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="1">
-        <v>4</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0</v>
-      </c>
-      <c r="D40" s="1">
-        <v>6</v>
-      </c>
-      <c r="E40" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D40,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2</v>
-      </c>
-      <c r="G40" s="1">
-        <v>30</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="1">
-        <v>4</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0</v>
-      </c>
-      <c r="D41" s="1">
-        <v>6</v>
-      </c>
-      <c r="E41" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D41,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1">
-        <v>40</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="1">
-        <v>4</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0</v>
-      </c>
-      <c r="D42" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E42" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D42,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F42" s="1">
-        <v>100</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="1">
-        <v>4</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E43" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D43,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F43" s="1">
-        <v>100</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
-        <v>0</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="1">
-        <v>4</v>
-      </c>
-      <c r="B44" s="1">
-        <v>2</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0</v>
-      </c>
-      <c r="D44" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E44" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D44,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F44" s="1">
-        <v>100</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="1">
-        <v>4</v>
-      </c>
-      <c r="B45" s="1">
-        <v>2</v>
-      </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E45" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D45,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F45" s="1">
-        <v>100</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
-      </c>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="1">
-        <v>4</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2</v>
-      </c>
-      <c r="C46" s="1">
-        <v>2</v>
-      </c>
-      <c r="D46" s="1">
-        <v>9</v>
-      </c>
-      <c r="E46" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D46,Define!I:I))</f>
-        <v>Shop</v>
-      </c>
-      <c r="F46" s="1">
-        <v>100</v>
-      </c>
-      <c r="G46" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="1">
-        <v>4</v>
-      </c>
-      <c r="B47" s="1">
-        <v>3</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0</v>
-      </c>
-      <c r="D47" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E47" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D47,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F47" s="1">
-        <v>100</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>0</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="1">
-        <v>4</v>
-      </c>
-      <c r="B48" s="1">
-        <v>3</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E48" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D48,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F48" s="1">
-        <v>100</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0</v>
-      </c>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="1">
-        <v>4</v>
-      </c>
-      <c r="B49" s="1">
-        <v>4</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D49,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F49" s="1">
-        <v>100</v>
-      </c>
-      <c r="G49" s="1">
-        <v>4041</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>4041</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="1">
-        <v>4</v>
-      </c>
-      <c r="B50" s="1">
-        <v>4</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D50,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F50" s="1">
-        <v>100</v>
-      </c>
-      <c r="G50" s="1">
-        <v>4042</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="1">
-        <v>4042</v>
-      </c>
-      <c r="J50" s="1">
-        <v>2</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="1">
-        <v>4</v>
-      </c>
-      <c r="B51" s="1">
-        <v>5</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1">
-        <v>6</v>
-      </c>
-      <c r="E51" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D51,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F51" s="1">
-        <v>100</v>
-      </c>
-      <c r="G51" s="1">
-        <v>40</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="1">
-        <v>4</v>
-      </c>
-      <c r="B52" s="1">
-        <v>5</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1">
-        <v>4</v>
-      </c>
-      <c r="E52" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D52,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F52" s="1">
-        <v>100</v>
-      </c>
-      <c r="G52" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H52" s="1">
-        <v>20</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="1">
-        <v>4</v>
-      </c>
-      <c r="B53" s="1">
-        <v>6</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0</v>
-      </c>
-      <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D53,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F53" s="1">
-        <v>100</v>
-      </c>
-      <c r="G53" s="1">
-        <v>4101</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="1">
-        <v>4101</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="1">
-        <v>4</v>
-      </c>
-      <c r="B54" s="1">
-        <v>6</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D54,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F54" s="1">
-        <v>100</v>
-      </c>
-      <c r="G54" s="1">
-        <v>4102</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="1">
-        <v>4102</v>
-      </c>
-      <c r="J54" s="1">
-        <v>2</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="1">
-        <v>4</v>
-      </c>
-      <c r="B55" s="1">
-        <v>7</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0</v>
-      </c>
-      <c r="D55" s="1">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D55,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F55" s="1">
-        <v>100</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="1">
-        <v>4</v>
-      </c>
-      <c r="B56" s="1">
-        <v>7</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="1">
-        <v>4</v>
-      </c>
-      <c r="E56" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D56,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F56" s="1">
-        <v>100</v>
-      </c>
-      <c r="G56" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H56" s="1">
-        <v>200</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="1">
-        <v>5</v>
-      </c>
-      <c r="B57" s="1">
-        <v>0</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1</v>
-      </c>
-      <c r="E57" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D57,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F57" s="1">
-        <v>80</v>
-      </c>
-      <c r="G57" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="1">
-        <v>5</v>
-      </c>
-      <c r="B58" s="1">
-        <v>0</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0</v>
-      </c>
-      <c r="D58" s="1">
-        <v>5</v>
-      </c>
-      <c r="E58" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D58,Define!I:I))</f>
-        <v>Actor</v>
-      </c>
-      <c r="F58" s="1">
-        <v>1</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="1">
-        <v>5</v>
-      </c>
-      <c r="B59" s="1">
-        <v>0</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0</v>
-      </c>
-      <c r="D59" s="1">
-        <v>8</v>
-      </c>
-      <c r="E59" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D59,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F59" s="1">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>252</v>
-      </c>
-      <c r="J59" s="1">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="1">
-        <v>5</v>
-      </c>
-      <c r="B60" s="1">
-        <v>0</v>
-      </c>
-      <c r="C60" s="1">
-        <v>0</v>
-      </c>
-      <c r="D60" s="1">
-        <v>6</v>
-      </c>
-      <c r="E60" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D60,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F60" s="1">
-        <v>4</v>
-      </c>
-      <c r="G60" s="1">
-        <v>20</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="1">
-        <v>5</v>
-      </c>
-      <c r="B61" s="1">
-        <v>0</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0</v>
-      </c>
-      <c r="D61" s="1">
-        <v>6</v>
-      </c>
-      <c r="E61" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D61,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F61" s="1">
-        <v>2</v>
-      </c>
-      <c r="G61" s="1">
-        <v>30</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="1">
-        <v>5</v>
-      </c>
-      <c r="B62" s="1">
-        <v>0</v>
-      </c>
-      <c r="C62" s="1">
-        <v>0</v>
-      </c>
-      <c r="D62" s="1">
-        <v>6</v>
-      </c>
-      <c r="E62" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D62,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F62" s="1">
-        <v>1</v>
-      </c>
-      <c r="G62" s="1">
-        <v>40</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="1">
-        <v>5</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0</v>
-      </c>
-      <c r="D63" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E63" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D63,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F63" s="1">
-        <v>100</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0</v>
-      </c>
-      <c r="I63" s="1">
-        <v>0</v>
-      </c>
-      <c r="J63" s="1">
-        <v>0</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="1">
-        <v>5</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E64" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D64,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F64" s="1">
-        <v>100</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1">
-        <v>0</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="1">
-        <v>5</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0</v>
-      </c>
-      <c r="D65" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E65" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D65,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F65" s="1">
-        <v>100</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="1">
-        <v>5</v>
-      </c>
-      <c r="B66" s="1">
-        <v>2</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E66" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D66,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F66" s="1">
-        <v>100</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="1">
-        <v>5</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2</v>
-      </c>
-      <c r="C67" s="1">
-        <v>2</v>
-      </c>
-      <c r="D67" s="1">
-        <v>9</v>
-      </c>
-      <c r="E67" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D67,Define!I:I))</f>
-        <v>Shop</v>
-      </c>
-      <c r="F67" s="1">
-        <v>100</v>
-      </c>
-      <c r="G67" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="1">
-        <v>5</v>
-      </c>
-      <c r="B68" s="1">
-        <v>3</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0</v>
-      </c>
-      <c r="D68" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E68" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D68,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F68" s="1">
-        <v>100</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="1">
-        <v>5</v>
-      </c>
-      <c r="B69" s="1">
-        <v>3</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E69" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D69,Define!I:I))</f>
-        <v>Random</v>
-      </c>
-      <c r="F69" s="1">
-        <v>100</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
-      <c r="I69" s="1">
-        <v>0</v>
-      </c>
-      <c r="J69" s="1">
-        <v>0</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="1">
-        <v>5</v>
-      </c>
-      <c r="B70" s="1">
-        <v>4</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D70,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F70" s="1">
-        <v>100</v>
-      </c>
-      <c r="G70" s="1">
-        <v>5041</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-      <c r="I70" s="1">
-        <v>5041</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="1">
-        <v>5</v>
-      </c>
-      <c r="B71" s="1">
-        <v>4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D71,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F71" s="1">
-        <v>100</v>
-      </c>
-      <c r="G71" s="1">
-        <v>5042</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
-      <c r="I71" s="1">
-        <v>5042</v>
-      </c>
-      <c r="J71" s="1">
-        <v>2</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="1">
-        <v>5</v>
-      </c>
-      <c r="B72" s="1">
-        <v>5</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0</v>
-      </c>
-      <c r="D72" s="1">
-        <v>6</v>
-      </c>
-      <c r="E72" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D72,Define!I:I))</f>
-        <v>Resource</v>
-      </c>
-      <c r="F72" s="1">
-        <v>100</v>
-      </c>
-      <c r="G72" s="1">
-        <v>50</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
-      <c r="I72" s="1">
-        <v>0</v>
-      </c>
-      <c r="J72" s="1">
-        <v>0</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="1">
-        <v>5</v>
-      </c>
-      <c r="B73" s="1">
-        <v>5</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="1">
-        <v>4</v>
-      </c>
-      <c r="E73" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D73,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F73" s="1">
-        <v>100</v>
-      </c>
-      <c r="G73" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H73" s="1">
-        <v>20</v>
-      </c>
-      <c r="I73" s="1">
-        <v>0</v>
-      </c>
-      <c r="J73" s="1">
-        <v>0</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="1">
-        <v>5</v>
-      </c>
-      <c r="B74" s="1">
-        <v>6</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0</v>
-      </c>
-      <c r="D74" s="1">
-        <v>2</v>
-      </c>
-      <c r="E74" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D74,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F74" s="1">
-        <v>100</v>
-      </c>
-      <c r="G74" s="1">
-        <v>5101</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0</v>
-      </c>
-      <c r="I74" s="1">
-        <v>5101</v>
-      </c>
-      <c r="J74" s="1">
-        <v>0</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="1">
-        <v>5</v>
-      </c>
-      <c r="B75" s="1">
-        <v>6</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="1">
-        <v>2</v>
-      </c>
-      <c r="E75" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D75,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F75" s="1">
-        <v>100</v>
-      </c>
-      <c r="G75" s="1">
-        <v>5102</v>
-      </c>
-      <c r="H75" s="1">
-        <v>0</v>
-      </c>
-      <c r="I75" s="1">
-        <v>5102</v>
-      </c>
-      <c r="J75" s="1">
-        <v>2</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="1">
-        <v>5</v>
-      </c>
-      <c r="B76" s="1">
-        <v>7</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0</v>
-      </c>
-      <c r="D76" s="1">
-        <v>4</v>
-      </c>
-      <c r="E76" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D76,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F76" s="1">
-        <v>100</v>
-      </c>
-      <c r="G76" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H76" s="1">
-        <v>20</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="1">
-        <v>5</v>
-      </c>
-      <c r="B77" s="1">
-        <v>7</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="1">
-        <v>4</v>
-      </c>
-      <c r="E77" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D77,Define!I:I))</f>
-        <v>Alcana</v>
-      </c>
-      <c r="F77" s="1">
-        <v>100</v>
-      </c>
-      <c r="G77" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H77" s="1">
-        <v>210</v>
-      </c>
-      <c r="I77" s="1">
-        <v>0</v>
-      </c>
-      <c r="J77" s="1">
-        <v>0</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="1">
-        <v>6</v>
-      </c>
-      <c r="B78" s="1">
-        <v>1</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0</v>
-      </c>
-      <c r="D78" s="1">
-        <v>8</v>
-      </c>
-      <c r="E78" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D78,Define!I:I))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="F78" s="1">
-        <v>100</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0</v>
-      </c>
-      <c r="H78" s="1">
-        <v>0</v>
-      </c>
-      <c r="I78" s="1">
-        <v>0</v>
-      </c>
-      <c r="J78" s="1">
-        <v>0</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="1">
-        <v>6</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1</v>
-      </c>
-      <c r="C79" s="1">
-        <v>1</v>
-      </c>
-      <c r="D79" s="1">
-        <v>9</v>
-      </c>
-      <c r="E79" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D79,Define!I:I))</f>
-        <v>Shop</v>
-      </c>
-      <c r="F79" s="1">
-        <v>100</v>
-      </c>
-      <c r="G79" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0</v>
-      </c>
-      <c r="J79" s="1">
-        <v>0</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="1">
-        <v>6</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0</v>
-      </c>
-      <c r="D80" s="1">
-        <v>1</v>
-      </c>
-      <c r="E80" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D80,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F80" s="1">
-        <v>100</v>
-      </c>
-      <c r="G80" s="1">
-        <v>6021</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0</v>
-      </c>
-      <c r="I80" s="1">
-        <v>6021</v>
-      </c>
-      <c r="J80" s="1">
-        <v>0</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="1">
-        <v>6</v>
-      </c>
-      <c r="B81" s="1">
-        <v>2</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
-      </c>
-      <c r="E81" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D81,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F81" s="1">
-        <v>100</v>
-      </c>
-      <c r="G81" s="1">
-        <v>6022</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
-      </c>
-      <c r="I81" s="1">
-        <v>6022</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="1">
-        <v>6</v>
-      </c>
-      <c r="B82" s="1">
-        <v>3</v>
-      </c>
-      <c r="C82" s="1">
-        <v>0</v>
-      </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D82,Define!I:I))</f>
-        <v>Battle</v>
-      </c>
-      <c r="F82" s="1">
-        <v>100</v>
-      </c>
-      <c r="G82">
-        <v>6031</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>6031</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82"/>
+      <c r="H82" s="1"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82" s="1"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="1">
-        <v>6</v>
-      </c>
-      <c r="B83" s="1">
-        <v>4</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0</v>
-      </c>
-      <c r="D83" s="1">
-        <v>2</v>
-      </c>
-      <c r="E83" s="1" t="str">
-        <f>INDEX(Define!J:J,MATCH(D83,Define!I:I))</f>
-        <v>Boss</v>
-      </c>
-      <c r="F83" s="1">
-        <v>100</v>
-      </c>
-      <c r="G83" s="1">
-        <v>6101</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1">
-        <v>6101</v>
-      </c>
-      <c r="J83" s="1">
-        <v>0</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5166,7 +3525,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>29</v>
@@ -5670,19 +4029,19 @@
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5706,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:3">
@@ -5717,10 +4076,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="39" spans="1:4">
@@ -5728,10 +4087,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -5740,10 +4099,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -5752,10 +4111,10 @@
         <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -5764,10 +4123,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -5776,10 +4135,10 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -5788,10 +4147,10 @@
         <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -5800,10 +4159,10 @@
         <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="39" spans="1:3">
@@ -5811,10 +4170,10 @@
         <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
@@ -5822,10 +4181,10 @@
         <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
@@ -5833,10 +4192,10 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
@@ -5844,10 +4203,10 @@
         <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5855,10 +4214,10 @@
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5866,10 +4225,10 @@
         <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5877,10 +4236,10 @@
         <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5888,10 +4247,10 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5925,19 +4284,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -5945,13 +4304,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -5962,19 +4321,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -5982,19 +4341,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -6002,19 +4361,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -6022,19 +4381,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:10">
@@ -6042,19 +4401,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -6062,13 +4421,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -6076,13 +4435,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -6090,13 +4449,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -6104,13 +4463,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -6118,13 +4477,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -6132,7 +4491,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -6140,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -6148,7 +4507,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -6156,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -6164,7 +4523,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -6172,7 +4531,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -6180,7 +4539,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -6188,7 +4547,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -6196,7 +4555,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -6204,7 +4563,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -6212,7 +4571,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -6220,7 +4579,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -136,10 +136,10 @@
     <t>バトル</t>
   </si>
   <si>
+    <t>シイナ加入</t>
+  </si>
+  <si>
     <t>魔法入手</t>
-  </si>
-  <si>
-    <t>シイナ加入</t>
   </si>
   <si>
     <t>バトル(ハード)</t>
@@ -576,9 +576,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -595,10 +595,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -609,8 +610,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -625,22 +673,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -653,24 +686,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -678,14 +695,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -702,23 +711,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -739,6 +732,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="ＭＳ ゴシック"/>
       <charset val="134"/>
@@ -753,7 +753,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,13 +777,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -783,13 +831,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,67 +873,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -879,36 +897,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -921,19 +909,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,8 +950,49 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -971,28 +1012,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1016,30 +1040,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -1052,145 +1052,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2191,23 +2191,23 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D5,Define!I:I))</f>
-        <v>Alcana</v>
+        <v>Event</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
       </c>
       <c r="G5" s="1">
-        <v>1021</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>1021</v>
+        <v>1041</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -2267,23 +2267,23 @@
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="str">
         <f>INDEX(Define!J:J,MATCH(D7,Define!I:I))</f>
-        <v>Event</v>
+        <v>Alcana</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
       </c>
       <c r="G7" s="1">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>1041</v>
+        <v>1021</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -3159,7 +3159,6 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -3492,10 +3491,7 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82"/>
       <c r="H82" s="1"/>
-      <c r="I82"/>
-      <c r="J82"/>
       <c r="K82" s="1"/>
     </row>
     <row r="83" spans="1:11">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="661"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="128">
   <si>
     <t>Id</t>
   </si>
@@ -83,6 +83,24 @@
   </si>
   <si>
     <t>stage9</t>
+  </si>
+  <si>
+    <t>stage10</t>
+  </si>
+  <si>
+    <t>stage11</t>
+  </si>
+  <si>
+    <t>stage12</t>
+  </si>
+  <si>
+    <t>stage13</t>
+  </si>
+  <si>
+    <t>stage14</t>
+  </si>
+  <si>
+    <t>stage15</t>
   </si>
   <si>
     <t>Turns</t>
@@ -578,8 +596,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -603,15 +621,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -619,30 +630,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -651,14 +639,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -680,7 +660,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -693,11 +711,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -709,9 +734,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -725,15 +749,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -753,7 +771,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,7 +813,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,37 +885,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,61 +897,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -891,25 +915,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,7 +927,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -934,6 +946,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,13 +974,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -978,6 +1000,35 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -998,30 +1049,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1035,15 +1062,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1052,16 +1070,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1070,127 +1088,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1529,7 +1547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="4" max="4" width="8.45454545454546" customWidth="1"/>
@@ -1599,10 +1617,10 @@
         <v>15</v>
       </c>
       <c r="I2" s="1">
-        <v>3</v>
+        <v>1010</v>
       </c>
       <c r="J2" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -1634,10 +1652,10 @@
         <v>15</v>
       </c>
       <c r="I3" s="1">
-        <v>3</v>
+        <v>1010</v>
       </c>
       <c r="J3" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>12</v>
@@ -1669,10 +1687,10 @@
         <v>15</v>
       </c>
       <c r="I4" s="1">
-        <v>3</v>
+        <v>1020</v>
       </c>
       <c r="J4" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>13</v>
@@ -1704,10 +1722,10 @@
         <v>15</v>
       </c>
       <c r="I5" s="1">
-        <v>3</v>
+        <v>1030</v>
       </c>
       <c r="J5" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>14</v>
@@ -1739,10 +1757,10 @@
         <v>15</v>
       </c>
       <c r="I6" s="1">
-        <v>3</v>
+        <v>1040</v>
       </c>
       <c r="J6" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>15</v>
@@ -1774,10 +1792,10 @@
         <v>15</v>
       </c>
       <c r="I7" s="1">
-        <v>3</v>
+        <v>1050</v>
       </c>
       <c r="J7" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>16</v>
@@ -1809,10 +1827,10 @@
         <v>15</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>1060</v>
       </c>
       <c r="J8" s="1">
-        <v>16</v>
+        <v>2010</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>17</v>
@@ -1844,10 +1862,10 @@
         <v>15</v>
       </c>
       <c r="I9" s="1">
-        <v>3</v>
+        <v>1070</v>
       </c>
       <c r="J9" s="1">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>18</v>
@@ -1879,10 +1897,10 @@
         <v>15</v>
       </c>
       <c r="I10" s="1">
-        <v>3</v>
+        <v>1080</v>
       </c>
       <c r="J10" s="1">
-        <v>11</v>
+        <v>2020</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>19</v>
@@ -1914,13 +1932,223 @@
         <v>15</v>
       </c>
       <c r="I11" s="1">
-        <v>3</v>
+        <v>1090</v>
       </c>
       <c r="J11" s="1">
-        <v>11</v>
+        <v>2020</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>100</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1100</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
+        <v>110</v>
+      </c>
+      <c r="B13" s="1">
+        <v>110</v>
+      </c>
+      <c r="C13" s="1">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1110</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1">
+        <v>120</v>
+      </c>
+      <c r="B14" s="1">
+        <v>120</v>
+      </c>
+      <c r="C14" s="1">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>22</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1">
+        <v>15</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1120</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1">
+        <v>130</v>
+      </c>
+      <c r="B15" s="1">
+        <v>130</v>
+      </c>
+      <c r="C15" s="1">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>24</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1">
+        <v>15</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1130</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1">
+        <v>140</v>
+      </c>
+      <c r="B16" s="1">
+        <v>140</v>
+      </c>
+      <c r="C16" s="1">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>26</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>15</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1140</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>150</v>
+      </c>
+      <c r="B17" s="1">
+        <v>150</v>
+      </c>
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>28</v>
+      </c>
+      <c r="G17" s="1">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1">
+        <v>15</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1150</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1150</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1944,25 +2172,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -2038,29 +2266,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2099,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2137,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2175,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -2213,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2251,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2289,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2327,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2365,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2403,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2441,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3521,25 +3749,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4019,25 +4247,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4061,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:3">
@@ -4072,10 +4300,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="39" spans="1:4">
@@ -4083,10 +4311,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -4095,10 +4323,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -4107,10 +4335,10 @@
         <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -4119,10 +4347,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -4131,10 +4359,10 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -4143,10 +4371,10 @@
         <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -4155,10 +4383,10 @@
         <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="39" spans="1:3">
@@ -4166,10 +4394,10 @@
         <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
@@ -4177,10 +4405,10 @@
         <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:3">
@@ -4188,10 +4416,10 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
@@ -4199,10 +4427,10 @@
         <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4210,10 +4438,10 @@
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4221,10 +4449,10 @@
         <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4232,10 +4460,10 @@
         <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4243,10 +4471,10 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4266,13 +4494,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:10">
@@ -4280,19 +4508,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I2" s="1">
         <v>-1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
@@ -4300,13 +4528,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -4317,19 +4545,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:10">
@@ -4337,19 +4565,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:10">
@@ -4357,19 +4585,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -4377,19 +4605,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:10">
@@ -4397,19 +4625,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="4:10">
@@ -4417,13 +4645,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="4:10">
@@ -4431,13 +4659,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I10" s="1">
         <v>7</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="4:10">
@@ -4445,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I11" s="1">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="4:10">
@@ -4459,13 +4687,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I12" s="1">
         <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="4:10">
@@ -4473,13 +4701,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1">
         <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="4:5">
@@ -4487,7 +4715,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="4:5">
@@ -4495,7 +4723,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="4:5">
@@ -4503,7 +4731,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="4:5">
@@ -4511,7 +4739,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:5">
@@ -4519,7 +4747,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:5">
@@ -4527,7 +4755,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="4:5">
@@ -4535,7 +4763,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="4:5">
@@ -4543,7 +4771,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="4:5">
@@ -4551,7 +4779,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="4:5">
@@ -4559,7 +4787,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="4:5">
@@ -4567,7 +4795,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="4:5">
@@ -4575,7 +4803,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
